--- a/artfynd/A 60367-2025 artfynd.xlsx
+++ b/artfynd/A 60367-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130141062</v>
+        <v>130141111</v>
       </c>
       <c r="B2" t="n">
-        <v>97702</v>
+        <v>79095</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>408421</v>
+        <v>408452</v>
       </c>
       <c r="R2" t="n">
-        <v>6771953</v>
+        <v>6771936</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130141111</v>
+        <v>130141118</v>
       </c>
       <c r="B3" t="n">
         <v>79095</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>408452</v>
+        <v>408392</v>
       </c>
       <c r="R3" t="n">
-        <v>6771936</v>
+        <v>6771906</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130141118</v>
+        <v>130141171</v>
       </c>
       <c r="B4" t="n">
         <v>79095</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>408392</v>
+        <v>408023</v>
       </c>
       <c r="R4" t="n">
-        <v>6771906</v>
+        <v>6771952</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130141171</v>
+        <v>130141179</v>
       </c>
       <c r="B5" t="n">
         <v>79095</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>408023</v>
+        <v>408446</v>
       </c>
       <c r="R5" t="n">
-        <v>6771952</v>
+        <v>6771725</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130141179</v>
+        <v>130141190</v>
       </c>
       <c r="B6" t="n">
         <v>79095</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>408446</v>
+        <v>408513</v>
       </c>
       <c r="R6" t="n">
-        <v>6771725</v>
+        <v>6772199</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130141190</v>
+        <v>130141191</v>
       </c>
       <c r="B7" t="n">
         <v>79095</v>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>408513</v>
+        <v>408509</v>
       </c>
       <c r="R7" t="n">
-        <v>6772199</v>
+        <v>6772194</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,32 +1317,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130141191</v>
+        <v>130141062</v>
       </c>
       <c r="B8" t="n">
-        <v>79095</v>
+        <v>97702</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>408509</v>
+        <v>408421</v>
       </c>
       <c r="R8" t="n">
-        <v>6772194</v>
+        <v>6771953</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -2601,50 +2601,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130141053</v>
+        <v>130141201</v>
       </c>
       <c r="B20" t="n">
-        <v>57738</v>
+        <v>92296</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>1965</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Citronporing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Antrodiella citrinella</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä &amp; Ryvarden</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>408180</v>
+        <v>408238</v>
       </c>
       <c r="R20" t="n">
-        <v>6771921</v>
+        <v>6771897</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2676,7 +2671,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2686,7 +2681,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2713,32 +2708,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130141201</v>
+        <v>130141059</v>
       </c>
       <c r="B21" t="n">
-        <v>92296</v>
+        <v>92092</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1965</v>
+        <v>1209</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Citronporing</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Antrodiella citrinella</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Ryvarden</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2748,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>408238</v>
+        <v>408213</v>
       </c>
       <c r="R21" t="n">
-        <v>6771897</v>
+        <v>6771880</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2783,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2793,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2820,45 +2815,50 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130141059</v>
+        <v>130141053</v>
       </c>
       <c r="B22" t="n">
-        <v>92092</v>
+        <v>57738</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>408213</v>
+        <v>408180</v>
       </c>
       <c r="R22" t="n">
-        <v>6771880</v>
+        <v>6771921</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3355,54 +3355,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130141100</v>
+        <v>130141188</v>
       </c>
       <c r="B27" t="n">
-        <v>98831</v>
+        <v>79095</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>408055</v>
+        <v>408452</v>
       </c>
       <c r="R27" t="n">
-        <v>6772067</v>
+        <v>6772262</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3434,7 +3425,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3444,7 +3435,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3471,7 +3462,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130141188</v>
+        <v>130141114</v>
       </c>
       <c r="B28" t="n">
         <v>79095</v>
@@ -3506,10 +3497,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>408452</v>
+        <v>408422</v>
       </c>
       <c r="R28" t="n">
-        <v>6772262</v>
+        <v>6771930</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3541,7 +3532,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3551,7 +3542,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3578,45 +3569,54 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130141114</v>
+        <v>130141100</v>
       </c>
       <c r="B29" t="n">
-        <v>79095</v>
+        <v>98831</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>408422</v>
+        <v>408055</v>
       </c>
       <c r="R29" t="n">
-        <v>6771930</v>
+        <v>6772067</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3685,10 +3685,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130141178</v>
+        <v>130141042</v>
       </c>
       <c r="B30" t="n">
-        <v>79095</v>
+        <v>91639</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3696,21 +3696,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3720,10 +3720,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>408446</v>
+        <v>408420</v>
       </c>
       <c r="R30" t="n">
-        <v>6771720</v>
+        <v>6771911</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3765,7 +3765,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3792,7 +3792,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130141192</v>
+        <v>130141178</v>
       </c>
       <c r="B31" t="n">
         <v>79095</v>
@@ -3827,10 +3827,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>408522</v>
+        <v>408446</v>
       </c>
       <c r="R31" t="n">
-        <v>6772172</v>
+        <v>6771720</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3899,7 +3899,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130141122</v>
+        <v>130141192</v>
       </c>
       <c r="B32" t="n">
         <v>79095</v>
@@ -3934,10 +3934,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>408301</v>
+        <v>408522</v>
       </c>
       <c r="R32" t="n">
-        <v>6771872</v>
+        <v>6772172</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3969,7 +3969,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4006,7 +4006,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130141126</v>
+        <v>130141122</v>
       </c>
       <c r="B33" t="n">
         <v>79095</v>
@@ -4041,10 +4041,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>408233</v>
+        <v>408301</v>
       </c>
       <c r="R33" t="n">
-        <v>6771939</v>
+        <v>6771872</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4113,7 +4113,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130141187</v>
+        <v>130141126</v>
       </c>
       <c r="B34" t="n">
         <v>79095</v>
@@ -4148,10 +4148,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>408448</v>
+        <v>408233</v>
       </c>
       <c r="R34" t="n">
-        <v>6772196</v>
+        <v>6771939</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4183,7 +4183,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4220,10 +4220,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130141042</v>
+        <v>130141187</v>
       </c>
       <c r="B35" t="n">
-        <v>91639</v>
+        <v>79095</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4231,21 +4231,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4255,10 +4255,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>408420</v>
+        <v>408448</v>
       </c>
       <c r="R35" t="n">
-        <v>6771911</v>
+        <v>6772196</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4290,7 +4290,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4300,7 +4300,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -7665,45 +7665,54 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130141138</v>
+        <v>130141098</v>
       </c>
       <c r="B67" t="n">
-        <v>79095</v>
+        <v>98831</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>408043</v>
+        <v>408080</v>
       </c>
       <c r="R67" t="n">
-        <v>6772111</v>
+        <v>6772000</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7735,7 +7744,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7745,7 +7754,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7772,7 +7781,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130141112</v>
+        <v>130141138</v>
       </c>
       <c r="B68" t="n">
         <v>79095</v>
@@ -7807,10 +7816,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>408432</v>
+        <v>408043</v>
       </c>
       <c r="R68" t="n">
-        <v>6771948</v>
+        <v>6772111</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7842,7 +7851,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7852,7 +7861,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7879,7 +7888,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130141119</v>
+        <v>130141112</v>
       </c>
       <c r="B69" t="n">
         <v>79095</v>
@@ -7914,10 +7923,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>408380</v>
+        <v>408432</v>
       </c>
       <c r="R69" t="n">
-        <v>6771903</v>
+        <v>6771948</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7949,7 +7958,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7959,7 +7968,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7986,54 +7995,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130141098</v>
+        <v>130141119</v>
       </c>
       <c r="B70" t="n">
-        <v>98831</v>
+        <v>79095</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>408080</v>
+        <v>408380</v>
       </c>
       <c r="R70" t="n">
-        <v>6772000</v>
+        <v>6771903</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8065,7 +8065,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8209,10 +8209,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130141037</v>
+        <v>130141070</v>
       </c>
       <c r="B72" t="n">
-        <v>91603</v>
+        <v>97702</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8220,21 +8220,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5447</v>
+        <v>221945</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8244,10 +8244,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>408048</v>
+        <v>408455</v>
       </c>
       <c r="R72" t="n">
-        <v>6772154</v>
+        <v>6771788</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8279,7 +8279,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8289,7 +8289,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8316,45 +8316,50 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130141070</v>
+        <v>130141055</v>
       </c>
       <c r="B73" t="n">
-        <v>97702</v>
+        <v>57738</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>408455</v>
+        <v>408062</v>
       </c>
       <c r="R73" t="n">
-        <v>6771788</v>
+        <v>6771974</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8386,7 +8391,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8396,7 +8401,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8423,50 +8428,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130141055</v>
+        <v>130141037</v>
       </c>
       <c r="B74" t="n">
-        <v>57738</v>
+        <v>91603</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>408062</v>
+        <v>408048</v>
       </c>
       <c r="R74" t="n">
-        <v>6771974</v>
+        <v>6772154</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8508,7 +8508,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD74" t="b">

--- a/artfynd/A 60367-2025 artfynd.xlsx
+++ b/artfynd/A 60367-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130141111</v>
+        <v>130141062</v>
       </c>
       <c r="B2" t="n">
-        <v>79095</v>
+        <v>97702</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>408452</v>
+        <v>408421</v>
       </c>
       <c r="R2" t="n">
-        <v>6771936</v>
+        <v>6771953</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130141118</v>
+        <v>130141111</v>
       </c>
       <c r="B3" t="n">
         <v>79095</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>408392</v>
+        <v>408452</v>
       </c>
       <c r="R3" t="n">
-        <v>6771906</v>
+        <v>6771936</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130141171</v>
+        <v>130141118</v>
       </c>
       <c r="B4" t="n">
         <v>79095</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>408023</v>
+        <v>408392</v>
       </c>
       <c r="R4" t="n">
-        <v>6771952</v>
+        <v>6771906</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130141179</v>
+        <v>130141171</v>
       </c>
       <c r="B5" t="n">
         <v>79095</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>408446</v>
+        <v>408023</v>
       </c>
       <c r="R5" t="n">
-        <v>6771725</v>
+        <v>6771952</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130141190</v>
+        <v>130141179</v>
       </c>
       <c r="B6" t="n">
         <v>79095</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>408513</v>
+        <v>408446</v>
       </c>
       <c r="R6" t="n">
-        <v>6772199</v>
+        <v>6771725</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130141191</v>
+        <v>130141190</v>
       </c>
       <c r="B7" t="n">
         <v>79095</v>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>408509</v>
+        <v>408513</v>
       </c>
       <c r="R7" t="n">
-        <v>6772194</v>
+        <v>6772199</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,32 +1317,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130141062</v>
+        <v>130141191</v>
       </c>
       <c r="B8" t="n">
-        <v>97702</v>
+        <v>79095</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>408421</v>
+        <v>408509</v>
       </c>
       <c r="R8" t="n">
-        <v>6771953</v>
+        <v>6772194</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -3355,45 +3355,54 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130141188</v>
+        <v>130141100</v>
       </c>
       <c r="B27" t="n">
-        <v>79095</v>
+        <v>98831</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>408452</v>
+        <v>408055</v>
       </c>
       <c r="R27" t="n">
-        <v>6772262</v>
+        <v>6772067</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3425,7 +3434,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3435,7 +3444,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3462,7 +3471,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130141114</v>
+        <v>130141188</v>
       </c>
       <c r="B28" t="n">
         <v>79095</v>
@@ -3497,10 +3506,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>408422</v>
+        <v>408452</v>
       </c>
       <c r="R28" t="n">
-        <v>6771930</v>
+        <v>6772262</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3532,7 +3541,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3542,7 +3551,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3569,54 +3578,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130141100</v>
+        <v>130141114</v>
       </c>
       <c r="B29" t="n">
-        <v>98831</v>
+        <v>79095</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>408055</v>
+        <v>408422</v>
       </c>
       <c r="R29" t="n">
-        <v>6772067</v>
+        <v>6771930</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -5421,10 +5421,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130141128</v>
+        <v>130141105</v>
       </c>
       <c r="B46" t="n">
-        <v>79095</v>
+        <v>91653</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5432,21 +5432,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5456,10 +5456,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>408213</v>
+        <v>408032</v>
       </c>
       <c r="R46" t="n">
-        <v>6771880</v>
+        <v>6772075</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5491,7 +5491,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5528,7 +5528,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130141184</v>
+        <v>130141128</v>
       </c>
       <c r="B47" t="n">
         <v>79095</v>
@@ -5563,10 +5563,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>408448</v>
+        <v>408213</v>
       </c>
       <c r="R47" t="n">
-        <v>6771990</v>
+        <v>6771880</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5608,7 +5608,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5635,7 +5635,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130141123</v>
+        <v>130141184</v>
       </c>
       <c r="B48" t="n">
         <v>79095</v>
@@ -5670,10 +5670,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>408291</v>
+        <v>408448</v>
       </c>
       <c r="R48" t="n">
-        <v>6771913</v>
+        <v>6771990</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5705,7 +5705,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5715,7 +5715,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5742,7 +5742,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130141120</v>
+        <v>130141123</v>
       </c>
       <c r="B49" t="n">
         <v>79095</v>
@@ -5777,10 +5777,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>408363</v>
+        <v>408291</v>
       </c>
       <c r="R49" t="n">
-        <v>6771889</v>
+        <v>6771913</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5812,7 +5812,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5822,7 +5822,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5849,32 +5849,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130141073</v>
+        <v>130141120</v>
       </c>
       <c r="B50" t="n">
-        <v>80228</v>
+        <v>79095</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5884,10 +5884,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>408029</v>
+        <v>408363</v>
       </c>
       <c r="R50" t="n">
-        <v>6771956</v>
+        <v>6771889</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5919,7 +5919,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5929,7 +5929,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5956,32 +5956,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130141105</v>
+        <v>130141103</v>
       </c>
       <c r="B51" t="n">
-        <v>91653</v>
+        <v>80166</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1204</v>
+        <v>229748</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5991,10 +5991,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>408032</v>
+        <v>408441</v>
       </c>
       <c r="R51" t="n">
-        <v>6772075</v>
+        <v>6771723</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6036,7 +6036,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6045,6 +6045,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6063,10 +6064,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130141103</v>
+        <v>130141073</v>
       </c>
       <c r="B52" t="n">
-        <v>80166</v>
+        <v>80228</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6074,21 +6075,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>229748</v>
+        <v>6461</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6098,10 +6099,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>408441</v>
+        <v>408029</v>
       </c>
       <c r="R52" t="n">
-        <v>6771723</v>
+        <v>6771956</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6133,7 +6134,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6143,7 +6144,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6152,7 +6153,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 60367-2025 artfynd.xlsx
+++ b/artfynd/A 60367-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130141062</v>
       </c>
       <c r="B2" t="n">
-        <v>97702</v>
+        <v>97704</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>130141045</v>
       </c>
       <c r="B9" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>130141068</v>
       </c>
       <c r="B19" t="n">
-        <v>97702</v>
+        <v>97704</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>130141201</v>
       </c>
       <c r="B20" t="n">
-        <v>92296</v>
+        <v>92298</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>130141059</v>
       </c>
       <c r="B21" t="n">
-        <v>92092</v>
+        <v>92094</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2815,10 +2815,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130141053</v>
+        <v>130141130</v>
       </c>
       <c r="B22" t="n">
-        <v>57738</v>
+        <v>79095</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2826,39 +2826,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>408180</v>
+        <v>408179</v>
       </c>
       <c r="R22" t="n">
-        <v>6771921</v>
+        <v>6771918</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2927,32 +2922,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130141130</v>
+        <v>130141041</v>
       </c>
       <c r="B23" t="n">
-        <v>79095</v>
+        <v>91605</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2962,10 +2957,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>408179</v>
+        <v>408520</v>
       </c>
       <c r="R23" t="n">
-        <v>6771918</v>
+        <v>6772210</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2997,7 +2992,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3007,7 +3002,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3034,45 +3029,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130141041</v>
+        <v>130141053</v>
       </c>
       <c r="B24" t="n">
-        <v>91603</v>
+        <v>57738</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>408520</v>
+        <v>408180</v>
       </c>
       <c r="R24" t="n">
-        <v>6772210</v>
+        <v>6771921</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3104,7 +3104,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3144,7 +3144,7 @@
         <v>130141049</v>
       </c>
       <c r="B25" t="n">
-        <v>91590</v>
+        <v>91592</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         <v>130141043</v>
       </c>
       <c r="B26" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3355,54 +3355,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130141100</v>
+        <v>130141188</v>
       </c>
       <c r="B27" t="n">
-        <v>98831</v>
+        <v>79095</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>408055</v>
+        <v>408452</v>
       </c>
       <c r="R27" t="n">
-        <v>6772067</v>
+        <v>6772262</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3434,7 +3425,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3444,7 +3435,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3471,7 +3462,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130141188</v>
+        <v>130141114</v>
       </c>
       <c r="B28" t="n">
         <v>79095</v>
@@ -3506,10 +3497,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>408452</v>
+        <v>408422</v>
       </c>
       <c r="R28" t="n">
-        <v>6772262</v>
+        <v>6771930</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3541,7 +3532,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3551,7 +3542,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3578,45 +3569,54 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130141114</v>
+        <v>130141100</v>
       </c>
       <c r="B29" t="n">
-        <v>79095</v>
+        <v>98833</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>408422</v>
+        <v>408055</v>
       </c>
       <c r="R29" t="n">
-        <v>6771930</v>
+        <v>6772067</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3688,7 +3688,7 @@
         <v>130141042</v>
       </c>
       <c r="B30" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4327,45 +4327,54 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130141038</v>
+        <v>130141096</v>
       </c>
       <c r="B36" t="n">
-        <v>91603</v>
+        <v>98833</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>408067</v>
+        <v>408022</v>
       </c>
       <c r="R36" t="n">
-        <v>6772053</v>
+        <v>6772065</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4397,7 +4406,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4407,7 +4416,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4434,54 +4443,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130141096</v>
+        <v>130141038</v>
       </c>
       <c r="B37" t="n">
-        <v>98831</v>
+        <v>91605</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>408022</v>
+        <v>408067</v>
       </c>
       <c r="R37" t="n">
-        <v>6772065</v>
+        <v>6772053</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4513,7 +4513,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4523,7 +4523,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4764,54 +4764,41 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130141101</v>
+        <v>130141108</v>
       </c>
       <c r="B40" t="n">
-        <v>98831</v>
+        <v>91661</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>408032</v>
+        <v>408452</v>
       </c>
       <c r="R40" t="n">
-        <v>6772075</v>
+        <v>6771915</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4843,7 +4830,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4853,7 +4840,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4880,38 +4867,42 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130141052</v>
+        <v>130141101</v>
       </c>
       <c r="B41" t="n">
-        <v>57738</v>
+        <v>98833</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4920,10 +4911,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>408232</v>
+        <v>408032</v>
       </c>
       <c r="R41" t="n">
-        <v>6771944</v>
+        <v>6772075</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4955,7 +4946,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4965,7 +4956,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4992,10 +4983,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130141108</v>
+        <v>130141052</v>
       </c>
       <c r="B42" t="n">
-        <v>91659</v>
+        <v>57738</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5003,30 +4994,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>408452</v>
+        <v>408232</v>
       </c>
       <c r="R42" t="n">
-        <v>6771915</v>
+        <v>6771944</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5205,7 +5205,7 @@
         <v>130141060</v>
       </c>
       <c r="B44" t="n">
-        <v>92092</v>
+        <v>92094</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5424,7 +5424,7 @@
         <v>130141105</v>
       </c>
       <c r="B46" t="n">
-        <v>91653</v>
+        <v>91655</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5742,32 +5742,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130141123</v>
+        <v>130141073</v>
       </c>
       <c r="B49" t="n">
-        <v>79095</v>
+        <v>80228</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5777,10 +5777,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>408291</v>
+        <v>408029</v>
       </c>
       <c r="R49" t="n">
-        <v>6771913</v>
+        <v>6771956</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5812,7 +5812,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5822,7 +5822,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5849,7 +5849,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130141120</v>
+        <v>130141123</v>
       </c>
       <c r="B50" t="n">
         <v>79095</v>
@@ -5884,10 +5884,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>408363</v>
+        <v>408291</v>
       </c>
       <c r="R50" t="n">
-        <v>6771889</v>
+        <v>6771913</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5919,7 +5919,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5929,7 +5929,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5956,32 +5956,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130141103</v>
+        <v>130141120</v>
       </c>
       <c r="B51" t="n">
-        <v>80166</v>
+        <v>79095</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>229748</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5991,10 +5991,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>408441</v>
+        <v>408363</v>
       </c>
       <c r="R51" t="n">
-        <v>6771723</v>
+        <v>6771889</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6036,7 +6036,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6045,7 +6045,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6064,10 +6063,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130141073</v>
+        <v>130141103</v>
       </c>
       <c r="B52" t="n">
-        <v>80228</v>
+        <v>80166</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6075,21 +6074,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6461</v>
+        <v>229748</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6099,10 +6098,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>408029</v>
+        <v>408441</v>
       </c>
       <c r="R52" t="n">
-        <v>6771956</v>
+        <v>6771723</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6134,7 +6133,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6144,7 +6143,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6153,6 +6152,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6171,10 +6171,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130141196</v>
+        <v>130141189</v>
       </c>
       <c r="B53" t="n">
-        <v>89038</v>
+        <v>79095</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6182,21 +6182,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6206,10 +6206,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>408233</v>
+        <v>408512</v>
       </c>
       <c r="R53" t="n">
-        <v>6771921</v>
+        <v>6772218</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6241,7 +6241,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6251,7 +6251,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6278,7 +6278,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130141189</v>
+        <v>130141135</v>
       </c>
       <c r="B54" t="n">
         <v>79095</v>
@@ -6313,10 +6313,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>408512</v>
+        <v>408031</v>
       </c>
       <c r="R54" t="n">
-        <v>6772218</v>
+        <v>6772014</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6348,7 +6348,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6358,7 +6358,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6385,7 +6385,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130141135</v>
+        <v>130141115</v>
       </c>
       <c r="B55" t="n">
         <v>79095</v>
@@ -6420,10 +6420,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>408031</v>
+        <v>408423</v>
       </c>
       <c r="R55" t="n">
-        <v>6772014</v>
+        <v>6771906</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6455,7 +6455,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6492,7 +6492,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130141115</v>
+        <v>130141117</v>
       </c>
       <c r="B56" t="n">
         <v>79095</v>
@@ -6527,10 +6527,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>408423</v>
+        <v>408409</v>
       </c>
       <c r="R56" t="n">
-        <v>6771906</v>
+        <v>6771881</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6572,7 +6572,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6599,7 +6599,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130141117</v>
+        <v>130141137</v>
       </c>
       <c r="B57" t="n">
         <v>79095</v>
@@ -6634,10 +6634,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>408409</v>
+        <v>408034</v>
       </c>
       <c r="R57" t="n">
-        <v>6771881</v>
+        <v>6772034</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6669,7 +6669,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6679,7 +6679,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6706,10 +6706,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130141137</v>
+        <v>130141196</v>
       </c>
       <c r="B58" t="n">
-        <v>79095</v>
+        <v>89038</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6717,21 +6717,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6741,10 +6741,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>408034</v>
+        <v>408233</v>
       </c>
       <c r="R58" t="n">
-        <v>6772034</v>
+        <v>6771921</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6776,7 +6776,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6786,7 +6786,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6816,7 +6816,7 @@
         <v>130141107</v>
       </c>
       <c r="B59" t="n">
-        <v>91659</v>
+        <v>91661</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6919,7 +6919,7 @@
         <v>130141064</v>
       </c>
       <c r="B60" t="n">
-        <v>97702</v>
+        <v>97704</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7023,10 +7023,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130141195</v>
+        <v>130141174</v>
       </c>
       <c r="B61" t="n">
-        <v>89038</v>
+        <v>79095</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7034,21 +7034,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7058,10 +7058,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>408282</v>
+        <v>408396</v>
       </c>
       <c r="R61" t="n">
-        <v>6771935</v>
+        <v>6771759</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7093,7 +7093,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7103,7 +7103,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7130,32 +7130,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130141040</v>
+        <v>130141195</v>
       </c>
       <c r="B62" t="n">
-        <v>91603</v>
+        <v>89038</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5447</v>
+        <v>510</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7165,10 +7165,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>408073</v>
+        <v>408282</v>
       </c>
       <c r="R62" t="n">
-        <v>6772016</v>
+        <v>6771935</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7210,7 +7210,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7237,32 +7237,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130141174</v>
+        <v>130141040</v>
       </c>
       <c r="B63" t="n">
-        <v>79095</v>
+        <v>91605</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7272,10 +7272,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>408396</v>
+        <v>408073</v>
       </c>
       <c r="R63" t="n">
-        <v>6771759</v>
+        <v>6772016</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7307,7 +7307,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7347,7 +7347,7 @@
         <v>130141035</v>
       </c>
       <c r="B64" t="n">
-        <v>91603</v>
+        <v>91605</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7561,7 +7561,7 @@
         <v>130141071</v>
       </c>
       <c r="B66" t="n">
-        <v>97702</v>
+        <v>97704</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7665,54 +7665,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130141098</v>
+        <v>130141138</v>
       </c>
       <c r="B67" t="n">
-        <v>98831</v>
+        <v>79095</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>408080</v>
+        <v>408043</v>
       </c>
       <c r="R67" t="n">
-        <v>6772000</v>
+        <v>6772111</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7744,7 +7735,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7754,7 +7745,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7781,7 +7772,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130141138</v>
+        <v>130141112</v>
       </c>
       <c r="B68" t="n">
         <v>79095</v>
@@ -7816,10 +7807,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>408043</v>
+        <v>408432</v>
       </c>
       <c r="R68" t="n">
-        <v>6772111</v>
+        <v>6771948</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7851,7 +7842,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7861,7 +7852,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7888,7 +7879,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130141112</v>
+        <v>130141119</v>
       </c>
       <c r="B69" t="n">
         <v>79095</v>
@@ -7923,10 +7914,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>408432</v>
+        <v>408380</v>
       </c>
       <c r="R69" t="n">
-        <v>6771948</v>
+        <v>6771903</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7958,7 +7949,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7968,7 +7959,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7995,45 +7986,54 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130141119</v>
+        <v>130141098</v>
       </c>
       <c r="B70" t="n">
-        <v>79095</v>
+        <v>98833</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>408380</v>
+        <v>408080</v>
       </c>
       <c r="R70" t="n">
-        <v>6771903</v>
+        <v>6772000</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8065,7 +8065,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8102,10 +8102,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130141048</v>
+        <v>130141055</v>
       </c>
       <c r="B71" t="n">
-        <v>91639</v>
+        <v>57738</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8113,34 +8113,39 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>408067</v>
+        <v>408062</v>
       </c>
       <c r="R71" t="n">
-        <v>6772051</v>
+        <v>6771974</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8172,7 +8177,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8182,7 +8187,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8212,7 +8217,7 @@
         <v>130141070</v>
       </c>
       <c r="B72" t="n">
-        <v>97702</v>
+        <v>97704</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8316,10 +8321,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130141055</v>
+        <v>130141048</v>
       </c>
       <c r="B73" t="n">
-        <v>57738</v>
+        <v>91641</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8327,39 +8332,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>408062</v>
+        <v>408067</v>
       </c>
       <c r="R73" t="n">
-        <v>6771974</v>
+        <v>6772051</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8391,7 +8391,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8401,7 +8401,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8431,7 +8431,7 @@
         <v>130141037</v>
       </c>
       <c r="B74" t="n">
-        <v>91603</v>
+        <v>91605</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8535,10 +8535,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130141194</v>
+        <v>130141181</v>
       </c>
       <c r="B75" t="n">
-        <v>89038</v>
+        <v>79095</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8546,21 +8546,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8570,13 +8570,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>408303</v>
+        <v>408466</v>
       </c>
       <c r="R75" t="n">
-        <v>6771876</v>
+        <v>6771845</v>
       </c>
       <c r="S75" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8615,7 +8615,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8642,10 +8642,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130141181</v>
+        <v>130141194</v>
       </c>
       <c r="B76" t="n">
-        <v>79095</v>
+        <v>89038</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8653,21 +8653,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8677,13 +8677,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>408466</v>
+        <v>408303</v>
       </c>
       <c r="R76" t="n">
-        <v>6771845</v>
+        <v>6771876</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8722,7 +8722,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9190,7 +9190,7 @@
         <v>130141069</v>
       </c>
       <c r="B81" t="n">
-        <v>97702</v>
+        <v>97704</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9297,7 +9297,7 @@
         <v>130141063</v>
       </c>
       <c r="B82" t="n">
-        <v>97702</v>
+        <v>97704</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10153,7 +10153,7 @@
         <v>130141094</v>
       </c>
       <c r="B90" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>

--- a/artfynd/A 60367-2025 artfynd.xlsx
+++ b/artfynd/A 60367-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130141062</v>
+        <v>130141111</v>
       </c>
       <c r="B2" t="n">
-        <v>97704</v>
+        <v>79180</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>408421</v>
+        <v>408452</v>
       </c>
       <c r="R2" t="n">
-        <v>6771953</v>
+        <v>6771936</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130141111</v>
+        <v>130141118</v>
       </c>
       <c r="B3" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>408452</v>
+        <v>408392</v>
       </c>
       <c r="R3" t="n">
-        <v>6771936</v>
+        <v>6771906</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130141118</v>
+        <v>130141171</v>
       </c>
       <c r="B4" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>408392</v>
+        <v>408023</v>
       </c>
       <c r="R4" t="n">
-        <v>6771906</v>
+        <v>6771952</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130141171</v>
+        <v>130141179</v>
       </c>
       <c r="B5" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>408023</v>
+        <v>408446</v>
       </c>
       <c r="R5" t="n">
-        <v>6771952</v>
+        <v>6771725</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,32 +1103,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130141179</v>
+        <v>130141062</v>
       </c>
       <c r="B6" t="n">
-        <v>79095</v>
+        <v>97791</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>408446</v>
+        <v>408421</v>
       </c>
       <c r="R6" t="n">
-        <v>6771725</v>
+        <v>6771953</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1213,7 +1213,7 @@
         <v>130141190</v>
       </c>
       <c r="B7" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>130141191</v>
       </c>
       <c r="B8" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130141045</v>
+        <v>130141176</v>
       </c>
       <c r="B9" t="n">
-        <v>91641</v>
+        <v>79180</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1435,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>408208</v>
+        <v>408421</v>
       </c>
       <c r="R9" t="n">
-        <v>6771888</v>
+        <v>6771727</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1534,7 +1534,7 @@
         <v>130141134</v>
       </c>
       <c r="B10" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>130141185</v>
       </c>
       <c r="B11" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>130141109</v>
       </c>
       <c r="B12" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130141176</v>
+        <v>130141045</v>
       </c>
       <c r="B13" t="n">
-        <v>79095</v>
+        <v>91728</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>408421</v>
+        <v>408208</v>
       </c>
       <c r="R13" t="n">
-        <v>6771727</v>
+        <v>6771888</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1962,7 +1962,7 @@
         <v>130141182</v>
       </c>
       <c r="B14" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>130141169</v>
       </c>
       <c r="B15" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>130141125</v>
       </c>
       <c r="B16" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>130141133</v>
       </c>
       <c r="B17" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>130141180</v>
       </c>
       <c r="B18" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>130141068</v>
       </c>
       <c r="B19" t="n">
-        <v>97704</v>
+        <v>97791</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2601,32 +2601,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130141201</v>
+        <v>130141130</v>
       </c>
       <c r="B20" t="n">
-        <v>92298</v>
+        <v>79180</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1965</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Citronporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Antrodiella citrinella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Ryvarden</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2636,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>408238</v>
+        <v>408179</v>
       </c>
       <c r="R20" t="n">
-        <v>6771897</v>
+        <v>6771918</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2708,32 +2708,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130141059</v>
+        <v>130141041</v>
       </c>
       <c r="B21" t="n">
-        <v>92094</v>
+        <v>91692</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2743,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>408213</v>
+        <v>408520</v>
       </c>
       <c r="R21" t="n">
-        <v>6771880</v>
+        <v>6772210</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2815,32 +2815,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130141130</v>
+        <v>130141201</v>
       </c>
       <c r="B22" t="n">
-        <v>79095</v>
+        <v>92385</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1965</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Citronporing</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Antrodiella citrinella</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä &amp; Ryvarden</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>408179</v>
+        <v>408238</v>
       </c>
       <c r="R22" t="n">
-        <v>6771918</v>
+        <v>6771897</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2922,32 +2922,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130141041</v>
+        <v>130141059</v>
       </c>
       <c r="B23" t="n">
-        <v>91605</v>
+        <v>92181</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2957,10 +2957,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>408520</v>
+        <v>408213</v>
       </c>
       <c r="R23" t="n">
-        <v>6772210</v>
+        <v>6771880</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3032,7 +3032,7 @@
         <v>130141053</v>
       </c>
       <c r="B24" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3141,10 +3141,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130141049</v>
+        <v>130141188</v>
       </c>
       <c r="B25" t="n">
-        <v>91592</v>
+        <v>79180</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3152,21 +3152,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3176,10 +3176,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>408266</v>
+        <v>408452</v>
       </c>
       <c r="R25" t="n">
-        <v>6771955</v>
+        <v>6772262</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3211,7 +3211,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3248,10 +3248,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130141043</v>
+        <v>130141049</v>
       </c>
       <c r="B26" t="n">
-        <v>91641</v>
+        <v>91679</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3259,21 +3259,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>112</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3283,10 +3283,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>408279</v>
+        <v>408266</v>
       </c>
       <c r="R26" t="n">
-        <v>6771971</v>
+        <v>6771955</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3318,7 +3318,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3355,10 +3355,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130141188</v>
+        <v>130141043</v>
       </c>
       <c r="B27" t="n">
-        <v>79095</v>
+        <v>91728</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3366,21 +3366,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>408452</v>
+        <v>408279</v>
       </c>
       <c r="R27" t="n">
-        <v>6772262</v>
+        <v>6771971</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3425,7 +3425,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3462,45 +3462,54 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130141114</v>
+        <v>130141100</v>
       </c>
       <c r="B28" t="n">
-        <v>79095</v>
+        <v>98920</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>408422</v>
+        <v>408055</v>
       </c>
       <c r="R28" t="n">
-        <v>6771930</v>
+        <v>6772067</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3532,7 +3541,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3542,7 +3551,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3569,54 +3578,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130141100</v>
+        <v>130141114</v>
       </c>
       <c r="B29" t="n">
-        <v>98833</v>
+        <v>79180</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>408055</v>
+        <v>408422</v>
       </c>
       <c r="R29" t="n">
-        <v>6772067</v>
+        <v>6771930</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3685,10 +3685,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130141042</v>
+        <v>130141178</v>
       </c>
       <c r="B30" t="n">
-        <v>91641</v>
+        <v>79180</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3696,21 +3696,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3720,10 +3720,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>408420</v>
+        <v>408446</v>
       </c>
       <c r="R30" t="n">
-        <v>6771911</v>
+        <v>6771720</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3765,7 +3765,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3792,10 +3792,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130141178</v>
+        <v>130141042</v>
       </c>
       <c r="B31" t="n">
-        <v>79095</v>
+        <v>91728</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3803,21 +3803,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3827,10 +3827,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>408446</v>
+        <v>408420</v>
       </c>
       <c r="R31" t="n">
-        <v>6771720</v>
+        <v>6771911</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3902,7 +3902,7 @@
         <v>130141192</v>
       </c>
       <c r="B32" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4009,7 +4009,7 @@
         <v>130141122</v>
       </c>
       <c r="B33" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         <v>130141126</v>
       </c>
       <c r="B34" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         <v>130141187</v>
       </c>
       <c r="B35" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         <v>130141096</v>
       </c>
       <c r="B36" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4446,7 +4446,7 @@
         <v>130141038</v>
       </c>
       <c r="B37" t="n">
-        <v>91605</v>
+        <v>91692</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4553,7 +4553,7 @@
         <v>130141175</v>
       </c>
       <c r="B38" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         <v>130141136</v>
       </c>
       <c r="B39" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4764,41 +4764,54 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130141108</v>
+        <v>130141101</v>
       </c>
       <c r="B40" t="n">
-        <v>91661</v>
+        <v>98920</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>408452</v>
+        <v>408032</v>
       </c>
       <c r="R40" t="n">
-        <v>6771915</v>
+        <v>6772075</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4830,7 +4843,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4840,7 +4853,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4867,54 +4880,41 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130141101</v>
+        <v>130141108</v>
       </c>
       <c r="B41" t="n">
-        <v>98833</v>
+        <v>91748</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>408032</v>
+        <v>408452</v>
       </c>
       <c r="R41" t="n">
-        <v>6772075</v>
+        <v>6771915</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4946,7 +4946,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4986,7 +4986,7 @@
         <v>130141052</v>
       </c>
       <c r="B42" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         <v>130141113</v>
       </c>
       <c r="B43" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5202,45 +5202,50 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130141060</v>
+        <v>130141029</v>
       </c>
       <c r="B44" t="n">
-        <v>92094</v>
+        <v>5197</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1209</v>
+        <v>105930</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>408215</v>
+        <v>408243</v>
       </c>
       <c r="R44" t="n">
-        <v>6771888</v>
+        <v>6771879</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5272,7 +5277,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5282,7 +5287,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5309,50 +5314,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130141029</v>
+        <v>130141060</v>
       </c>
       <c r="B45" t="n">
-        <v>5197</v>
+        <v>92181</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>105930</v>
+        <v>1209</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>408243</v>
+        <v>408215</v>
       </c>
       <c r="R45" t="n">
-        <v>6771879</v>
+        <v>6771888</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5384,7 +5384,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5394,7 +5394,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5421,10 +5421,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130141105</v>
+        <v>130141184</v>
       </c>
       <c r="B46" t="n">
-        <v>91655</v>
+        <v>79180</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5432,21 +5432,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5456,10 +5456,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>408032</v>
+        <v>408448</v>
       </c>
       <c r="R46" t="n">
-        <v>6772075</v>
+        <v>6771990</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5491,7 +5491,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5531,7 +5531,7 @@
         <v>130141128</v>
       </c>
       <c r="B47" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5635,32 +5635,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130141184</v>
+        <v>130141073</v>
       </c>
       <c r="B48" t="n">
-        <v>79095</v>
+        <v>80313</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5670,10 +5670,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>408448</v>
+        <v>408029</v>
       </c>
       <c r="R48" t="n">
-        <v>6771990</v>
+        <v>6771956</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5705,7 +5705,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5715,7 +5715,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5742,32 +5742,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130141073</v>
+        <v>130141105</v>
       </c>
       <c r="B49" t="n">
-        <v>80228</v>
+        <v>91742</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6461</v>
+        <v>1204</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5777,10 +5777,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>408029</v>
+        <v>408032</v>
       </c>
       <c r="R49" t="n">
-        <v>6771956</v>
+        <v>6772075</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5812,7 +5812,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5822,7 +5822,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5852,7 +5852,7 @@
         <v>130141123</v>
       </c>
       <c r="B50" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5956,32 +5956,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130141120</v>
+        <v>130141103</v>
       </c>
       <c r="B51" t="n">
-        <v>79095</v>
+        <v>80251</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>229748</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5991,10 +5991,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>408363</v>
+        <v>408441</v>
       </c>
       <c r="R51" t="n">
-        <v>6771889</v>
+        <v>6771723</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6036,7 +6036,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6045,6 +6045,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6063,32 +6064,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130141103</v>
+        <v>130141120</v>
       </c>
       <c r="B52" t="n">
-        <v>80166</v>
+        <v>79180</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>229748</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6098,10 +6099,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>408441</v>
+        <v>408363</v>
       </c>
       <c r="R52" t="n">
-        <v>6771723</v>
+        <v>6771889</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6133,7 +6134,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6143,7 +6144,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6152,7 +6153,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6171,10 +6171,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130141189</v>
+        <v>130141196</v>
       </c>
       <c r="B53" t="n">
-        <v>79095</v>
+        <v>89125</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6182,21 +6182,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6206,10 +6206,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>408512</v>
+        <v>408233</v>
       </c>
       <c r="R53" t="n">
-        <v>6772218</v>
+        <v>6771921</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6241,7 +6241,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6251,7 +6251,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6278,10 +6278,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130141135</v>
+        <v>130141189</v>
       </c>
       <c r="B54" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6313,10 +6313,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>408031</v>
+        <v>408512</v>
       </c>
       <c r="R54" t="n">
-        <v>6772014</v>
+        <v>6772218</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6348,7 +6348,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6358,7 +6358,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6385,10 +6385,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130141115</v>
+        <v>130141135</v>
       </c>
       <c r="B55" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6420,10 +6420,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>408423</v>
+        <v>408031</v>
       </c>
       <c r="R55" t="n">
-        <v>6771906</v>
+        <v>6772014</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6455,7 +6455,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6492,10 +6492,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130141117</v>
+        <v>130141115</v>
       </c>
       <c r="B56" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6527,10 +6527,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>408409</v>
+        <v>408423</v>
       </c>
       <c r="R56" t="n">
-        <v>6771881</v>
+        <v>6771906</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6572,7 +6572,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6599,10 +6599,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130141137</v>
+        <v>130141117</v>
       </c>
       <c r="B57" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6634,10 +6634,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>408034</v>
+        <v>408409</v>
       </c>
       <c r="R57" t="n">
-        <v>6772034</v>
+        <v>6771881</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6669,7 +6669,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6679,7 +6679,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6706,10 +6706,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130141196</v>
+        <v>130141137</v>
       </c>
       <c r="B58" t="n">
-        <v>89038</v>
+        <v>79180</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6717,21 +6717,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6741,10 +6741,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>408233</v>
+        <v>408034</v>
       </c>
       <c r="R58" t="n">
-        <v>6771921</v>
+        <v>6772034</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6776,7 +6776,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6786,7 +6786,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6816,7 +6816,7 @@
         <v>130141107</v>
       </c>
       <c r="B59" t="n">
-        <v>91661</v>
+        <v>91748</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6919,7 +6919,7 @@
         <v>130141064</v>
       </c>
       <c r="B60" t="n">
-        <v>97704</v>
+        <v>97791</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7023,10 +7023,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130141174</v>
+        <v>130141195</v>
       </c>
       <c r="B61" t="n">
-        <v>79095</v>
+        <v>89125</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7034,21 +7034,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7058,10 +7058,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>408396</v>
+        <v>408282</v>
       </c>
       <c r="R61" t="n">
-        <v>6771759</v>
+        <v>6771935</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7093,7 +7093,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7103,7 +7103,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7130,32 +7130,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130141195</v>
+        <v>130141040</v>
       </c>
       <c r="B62" t="n">
-        <v>89038</v>
+        <v>91692</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>510</v>
+        <v>5447</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7165,10 +7165,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>408282</v>
+        <v>408073</v>
       </c>
       <c r="R62" t="n">
-        <v>6771935</v>
+        <v>6772016</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7210,7 +7210,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7237,32 +7237,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130141040</v>
+        <v>130141174</v>
       </c>
       <c r="B63" t="n">
-        <v>91605</v>
+        <v>79180</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7272,10 +7272,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>408073</v>
+        <v>408396</v>
       </c>
       <c r="R63" t="n">
-        <v>6772016</v>
+        <v>6771759</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7307,7 +7307,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7347,7 +7347,7 @@
         <v>130141035</v>
       </c>
       <c r="B64" t="n">
-        <v>91605</v>
+        <v>91692</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7454,7 +7454,7 @@
         <v>130141168</v>
       </c>
       <c r="B65" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7561,7 +7561,7 @@
         <v>130141071</v>
       </c>
       <c r="B66" t="n">
-        <v>97704</v>
+        <v>97791</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7665,45 +7665,54 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130141138</v>
+        <v>130141098</v>
       </c>
       <c r="B67" t="n">
-        <v>79095</v>
+        <v>98920</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>408043</v>
+        <v>408080</v>
       </c>
       <c r="R67" t="n">
-        <v>6772111</v>
+        <v>6772000</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7735,7 +7744,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7745,7 +7754,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7772,10 +7781,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130141112</v>
+        <v>130141138</v>
       </c>
       <c r="B68" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7807,10 +7816,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>408432</v>
+        <v>408043</v>
       </c>
       <c r="R68" t="n">
-        <v>6771948</v>
+        <v>6772111</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7842,7 +7851,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7852,7 +7861,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7879,10 +7888,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130141119</v>
+        <v>130141112</v>
       </c>
       <c r="B69" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7914,10 +7923,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>408380</v>
+        <v>408432</v>
       </c>
       <c r="R69" t="n">
-        <v>6771903</v>
+        <v>6771948</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7949,7 +7958,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7959,7 +7968,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7986,54 +7995,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130141098</v>
+        <v>130141119</v>
       </c>
       <c r="B70" t="n">
-        <v>98833</v>
+        <v>79180</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>408080</v>
+        <v>408380</v>
       </c>
       <c r="R70" t="n">
-        <v>6772000</v>
+        <v>6771903</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8065,7 +8065,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8102,50 +8102,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130141055</v>
+        <v>130141037</v>
       </c>
       <c r="B71" t="n">
-        <v>57738</v>
+        <v>91692</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>408062</v>
+        <v>408048</v>
       </c>
       <c r="R71" t="n">
-        <v>6771974</v>
+        <v>6772154</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8177,7 +8172,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8187,7 +8182,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8214,45 +8209,50 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130141070</v>
+        <v>130141055</v>
       </c>
       <c r="B72" t="n">
-        <v>97704</v>
+        <v>57823</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>408455</v>
+        <v>408062</v>
       </c>
       <c r="R72" t="n">
-        <v>6771788</v>
+        <v>6771974</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8284,7 +8284,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8321,32 +8321,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130141048</v>
+        <v>130141070</v>
       </c>
       <c r="B73" t="n">
-        <v>91641</v>
+        <v>97791</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8356,10 +8356,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>408067</v>
+        <v>408455</v>
       </c>
       <c r="R73" t="n">
-        <v>6772051</v>
+        <v>6771788</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8391,7 +8391,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8401,7 +8401,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8428,32 +8428,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130141037</v>
+        <v>130141048</v>
       </c>
       <c r="B74" t="n">
-        <v>91605</v>
+        <v>91728</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8463,10 +8463,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>408048</v>
+        <v>408067</v>
       </c>
       <c r="R74" t="n">
-        <v>6772154</v>
+        <v>6772051</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8508,7 +8508,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8538,7 +8538,7 @@
         <v>130141181</v>
       </c>
       <c r="B75" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8642,10 +8642,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130141194</v>
+        <v>130141129</v>
       </c>
       <c r="B76" t="n">
-        <v>89038</v>
+        <v>79180</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8653,21 +8653,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8677,13 +8677,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>408303</v>
+        <v>408199</v>
       </c>
       <c r="R76" t="n">
-        <v>6771876</v>
+        <v>6771896</v>
       </c>
       <c r="S76" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8722,7 +8722,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8749,10 +8749,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>130141129</v>
+        <v>130141116</v>
       </c>
       <c r="B77" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8784,10 +8784,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>408199</v>
+        <v>408411</v>
       </c>
       <c r="R77" t="n">
-        <v>6771896</v>
+        <v>6771863</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8819,7 +8819,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8829,7 +8829,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8856,10 +8856,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>130141116</v>
+        <v>130141061</v>
       </c>
       <c r="B78" t="n">
-        <v>79095</v>
+        <v>57826</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8867,34 +8867,39 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>408411</v>
+        <v>408232</v>
       </c>
       <c r="R78" t="n">
-        <v>6771863</v>
+        <v>6771933</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8926,7 +8931,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8936,7 +8941,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8966,7 +8976,7 @@
         <v>130141183</v>
       </c>
       <c r="B79" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9070,10 +9080,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>130141061</v>
+        <v>130141194</v>
       </c>
       <c r="B80" t="n">
-        <v>57741</v>
+        <v>89125</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9081,42 +9091,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>408232</v>
+        <v>408303</v>
       </c>
       <c r="R80" t="n">
-        <v>6771933</v>
+        <v>6771876</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9145,7 +9150,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9155,12 +9160,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:16</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9190,7 +9190,7 @@
         <v>130141069</v>
       </c>
       <c r="B81" t="n">
-        <v>97704</v>
+        <v>97791</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9297,7 +9297,7 @@
         <v>130141063</v>
       </c>
       <c r="B82" t="n">
-        <v>97704</v>
+        <v>97791</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         <v>130141186</v>
       </c>
       <c r="B83" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9511,7 +9511,7 @@
         <v>130141124</v>
       </c>
       <c r="B84" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9618,7 +9618,7 @@
         <v>130141131</v>
       </c>
       <c r="B85" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9722,45 +9722,54 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>130141173</v>
+        <v>130141094</v>
       </c>
       <c r="B86" t="n">
-        <v>79095</v>
+        <v>98920</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>408388</v>
+        <v>408187</v>
       </c>
       <c r="R86" t="n">
-        <v>6771760</v>
+        <v>6771901</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9792,7 +9801,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9802,7 +9811,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9829,10 +9838,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>130141177</v>
+        <v>130141173</v>
       </c>
       <c r="B87" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9864,10 +9873,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>408429</v>
+        <v>408388</v>
       </c>
       <c r="R87" t="n">
-        <v>6771723</v>
+        <v>6771760</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9899,7 +9908,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9909,7 +9918,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9936,10 +9945,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>130141170</v>
+        <v>130141177</v>
       </c>
       <c r="B88" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9971,10 +9980,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>408080</v>
+        <v>408429</v>
       </c>
       <c r="R88" t="n">
-        <v>6772000</v>
+        <v>6771723</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10006,7 +10015,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10016,7 +10025,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10043,10 +10052,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>130141110</v>
+        <v>130141170</v>
       </c>
       <c r="B89" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10078,10 +10087,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>408466</v>
+        <v>408080</v>
       </c>
       <c r="R89" t="n">
-        <v>6771924</v>
+        <v>6772000</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10113,7 +10122,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10123,7 +10132,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10150,54 +10159,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>130141094</v>
+        <v>130141110</v>
       </c>
       <c r="B90" t="n">
-        <v>98833</v>
+        <v>79180</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>408187</v>
+        <v>408466</v>
       </c>
       <c r="R90" t="n">
-        <v>6771901</v>
+        <v>6771924</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10229,7 +10229,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10239,7 +10239,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD90" t="b">

--- a/artfynd/A 60367-2025 artfynd.xlsx
+++ b/artfynd/A 60367-2025 artfynd.xlsx
@@ -3141,10 +3141,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130141049</v>
+        <v>130141043</v>
       </c>
       <c r="B25" t="n">
-        <v>91679</v>
+        <v>91728</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3152,21 +3152,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>112</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3176,10 +3176,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>408266</v>
+        <v>408279</v>
       </c>
       <c r="R25" t="n">
-        <v>6771955</v>
+        <v>6771971</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3211,7 +3211,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3248,10 +3248,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130141043</v>
+        <v>130141188</v>
       </c>
       <c r="B26" t="n">
-        <v>91728</v>
+        <v>79180</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3259,21 +3259,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3283,10 +3283,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>408279</v>
+        <v>408452</v>
       </c>
       <c r="R26" t="n">
-        <v>6771971</v>
+        <v>6772262</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3318,7 +3318,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3355,7 +3355,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130141188</v>
+        <v>130141114</v>
       </c>
       <c r="B27" t="n">
         <v>79180</v>
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>408452</v>
+        <v>408422</v>
       </c>
       <c r="R27" t="n">
-        <v>6772262</v>
+        <v>6771930</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3425,7 +3425,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3462,10 +3462,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130141114</v>
+        <v>130141049</v>
       </c>
       <c r="B28" t="n">
-        <v>79180</v>
+        <v>91679</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3473,21 +3473,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3497,10 +3497,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>408422</v>
+        <v>408266</v>
       </c>
       <c r="R28" t="n">
-        <v>6771930</v>
+        <v>6771955</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3532,7 +3532,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -7665,54 +7665,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130141098</v>
+        <v>130141119</v>
       </c>
       <c r="B67" t="n">
-        <v>98920</v>
+        <v>79180</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>408080</v>
+        <v>408380</v>
       </c>
       <c r="R67" t="n">
-        <v>6772000</v>
+        <v>6771903</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7744,7 +7735,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7754,7 +7745,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7781,7 +7772,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130141119</v>
+        <v>130141138</v>
       </c>
       <c r="B68" t="n">
         <v>79180</v>
@@ -7816,10 +7807,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>408380</v>
+        <v>408043</v>
       </c>
       <c r="R68" t="n">
-        <v>6771903</v>
+        <v>6772111</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7851,7 +7842,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7861,7 +7852,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7888,7 +7879,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130141138</v>
+        <v>130141112</v>
       </c>
       <c r="B69" t="n">
         <v>79180</v>
@@ -7923,10 +7914,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>408043</v>
+        <v>408432</v>
       </c>
       <c r="R69" t="n">
-        <v>6772111</v>
+        <v>6771948</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7958,7 +7949,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7968,7 +7959,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7995,45 +7986,54 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130141112</v>
+        <v>130141098</v>
       </c>
       <c r="B70" t="n">
-        <v>79180</v>
+        <v>98920</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>408432</v>
+        <v>408080</v>
       </c>
       <c r="R70" t="n">
-        <v>6771948</v>
+        <v>6772000</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8065,7 +8065,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9615,7 +9615,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>130141177</v>
+        <v>130141173</v>
       </c>
       <c r="B85" t="n">
         <v>79180</v>
@@ -9650,10 +9650,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>408429</v>
+        <v>408388</v>
       </c>
       <c r="R85" t="n">
-        <v>6771723</v>
+        <v>6771760</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9685,7 +9685,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9695,7 +9695,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9722,7 +9722,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>130141173</v>
+        <v>130141177</v>
       </c>
       <c r="B86" t="n">
         <v>79180</v>
@@ -9757,10 +9757,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>408388</v>
+        <v>408429</v>
       </c>
       <c r="R86" t="n">
-        <v>6771760</v>
+        <v>6771723</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9802,7 +9802,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD86" t="b">

--- a/artfynd/A 60367-2025 artfynd.xlsx
+++ b/artfynd/A 60367-2025 artfynd.xlsx
@@ -4764,45 +4764,54 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130141113</v>
+        <v>130141101</v>
       </c>
       <c r="B40" t="n">
-        <v>79180</v>
+        <v>98920</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>408416</v>
+        <v>408032</v>
       </c>
       <c r="R40" t="n">
-        <v>6771941</v>
+        <v>6772075</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4834,7 +4843,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4844,7 +4853,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4871,10 +4880,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130141052</v>
+        <v>130141113</v>
       </c>
       <c r="B41" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4882,39 +4891,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>408232</v>
+        <v>408416</v>
       </c>
       <c r="R41" t="n">
-        <v>6771944</v>
+        <v>6771941</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4946,7 +4950,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4956,7 +4960,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4983,54 +4987,41 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130141101</v>
+        <v>130141108</v>
       </c>
       <c r="B42" t="n">
-        <v>98920</v>
+        <v>91748</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>408032</v>
+        <v>408452</v>
       </c>
       <c r="R42" t="n">
-        <v>6772075</v>
+        <v>6771915</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5062,7 +5053,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5072,7 +5063,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5099,10 +5090,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130141108</v>
+        <v>130141052</v>
       </c>
       <c r="B43" t="n">
-        <v>91748</v>
+        <v>57823</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5110,30 +5101,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>408452</v>
+        <v>408232</v>
       </c>
       <c r="R43" t="n">
-        <v>6771915</v>
+        <v>6771944</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5165,7 +5165,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5175,7 +5175,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5421,32 +5421,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130141103</v>
+        <v>130141105</v>
       </c>
       <c r="B46" t="n">
-        <v>80251</v>
+        <v>91742</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>229748</v>
+        <v>1204</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5456,10 +5456,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>408441</v>
+        <v>408032</v>
       </c>
       <c r="R46" t="n">
-        <v>6771723</v>
+        <v>6772075</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5491,7 +5491,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5510,7 +5510,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5529,32 +5528,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130141105</v>
+        <v>130141073</v>
       </c>
       <c r="B47" t="n">
-        <v>91742</v>
+        <v>80313</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1204</v>
+        <v>6461</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5564,10 +5563,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>408032</v>
+        <v>408029</v>
       </c>
       <c r="R47" t="n">
-        <v>6772075</v>
+        <v>6771956</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5599,7 +5598,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5609,7 +5608,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6064,10 +6063,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130141073</v>
+        <v>130141103</v>
       </c>
       <c r="B52" t="n">
-        <v>80313</v>
+        <v>80251</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6075,21 +6074,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6461</v>
+        <v>229748</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6099,10 +6098,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>408029</v>
+        <v>408441</v>
       </c>
       <c r="R52" t="n">
-        <v>6771956</v>
+        <v>6771723</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6134,7 +6133,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6144,7 +6143,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6153,6 +6152,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6171,32 +6171,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130141196</v>
+        <v>130141064</v>
       </c>
       <c r="B53" t="n">
-        <v>89124</v>
+        <v>97791</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>510</v>
+        <v>221945</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6206,10 +6206,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>408233</v>
+        <v>408256</v>
       </c>
       <c r="R53" t="n">
-        <v>6771921</v>
+        <v>6771965</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6241,7 +6241,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6251,7 +6251,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6278,10 +6278,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130141107</v>
+        <v>130141196</v>
       </c>
       <c r="B54" t="n">
-        <v>91748</v>
+        <v>89124</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6289,19 +6289,23 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6309,10 +6313,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>408453</v>
+        <v>408233</v>
       </c>
       <c r="R54" t="n">
-        <v>6771936</v>
+        <v>6771921</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6344,7 +6348,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6354,7 +6358,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6916,34 +6920,30 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130141064</v>
+        <v>130141107</v>
       </c>
       <c r="B60" t="n">
-        <v>97791</v>
+        <v>91748</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -6951,10 +6951,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>408256</v>
+        <v>408453</v>
       </c>
       <c r="R60" t="n">
-        <v>6771965</v>
+        <v>6771936</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6986,7 +6986,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6996,7 +6996,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7665,45 +7665,54 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130141119</v>
+        <v>130141098</v>
       </c>
       <c r="B67" t="n">
-        <v>79180</v>
+        <v>98920</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>408380</v>
+        <v>408080</v>
       </c>
       <c r="R67" t="n">
-        <v>6771903</v>
+        <v>6772000</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7735,7 +7744,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7745,7 +7754,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7772,7 +7781,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130141138</v>
+        <v>130141119</v>
       </c>
       <c r="B68" t="n">
         <v>79180</v>
@@ -7807,10 +7816,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>408043</v>
+        <v>408380</v>
       </c>
       <c r="R68" t="n">
-        <v>6772111</v>
+        <v>6771903</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7842,7 +7851,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7852,7 +7861,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7879,7 +7888,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130141112</v>
+        <v>130141138</v>
       </c>
       <c r="B69" t="n">
         <v>79180</v>
@@ -7914,10 +7923,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>408432</v>
+        <v>408043</v>
       </c>
       <c r="R69" t="n">
-        <v>6771948</v>
+        <v>6772111</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7949,7 +7958,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7959,7 +7968,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7986,54 +7995,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130141098</v>
+        <v>130141112</v>
       </c>
       <c r="B70" t="n">
-        <v>98920</v>
+        <v>79180</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>408080</v>
+        <v>408432</v>
       </c>
       <c r="R70" t="n">
-        <v>6772000</v>
+        <v>6771948</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8065,7 +8065,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD70" t="b">

--- a/artfynd/A 60367-2025 artfynd.xlsx
+++ b/artfynd/A 60367-2025 artfynd.xlsx
@@ -4764,54 +4764,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130141101</v>
+        <v>130141113</v>
       </c>
       <c r="B40" t="n">
-        <v>98920</v>
+        <v>79180</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>408032</v>
+        <v>408416</v>
       </c>
       <c r="R40" t="n">
-        <v>6772075</v>
+        <v>6771941</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4843,7 +4834,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4853,7 +4844,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4880,10 +4871,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130141113</v>
+        <v>130141052</v>
       </c>
       <c r="B41" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4891,34 +4882,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>408416</v>
+        <v>408232</v>
       </c>
       <c r="R41" t="n">
-        <v>6771941</v>
+        <v>6771944</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4950,7 +4946,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4960,7 +4956,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4987,41 +4983,54 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130141108</v>
+        <v>130141101</v>
       </c>
       <c r="B42" t="n">
-        <v>91748</v>
+        <v>98920</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>408452</v>
+        <v>408032</v>
       </c>
       <c r="R42" t="n">
-        <v>6771915</v>
+        <v>6772075</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5053,7 +5062,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5063,7 +5072,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5090,10 +5099,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130141052</v>
+        <v>130141108</v>
       </c>
       <c r="B43" t="n">
-        <v>57823</v>
+        <v>91748</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5101,39 +5110,30 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>408232</v>
+        <v>408452</v>
       </c>
       <c r="R43" t="n">
-        <v>6771944</v>
+        <v>6771915</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5165,7 +5165,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5175,7 +5175,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6171,32 +6171,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130141064</v>
+        <v>130141196</v>
       </c>
       <c r="B53" t="n">
-        <v>97791</v>
+        <v>89124</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221945</v>
+        <v>510</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6206,10 +6206,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>408256</v>
+        <v>408233</v>
       </c>
       <c r="R53" t="n">
-        <v>6771965</v>
+        <v>6771921</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6241,7 +6241,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6251,7 +6251,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6278,10 +6278,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130141196</v>
+        <v>130141107</v>
       </c>
       <c r="B54" t="n">
-        <v>89124</v>
+        <v>91748</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6289,23 +6289,19 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6313,10 +6309,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>408233</v>
+        <v>408453</v>
       </c>
       <c r="R54" t="n">
-        <v>6771921</v>
+        <v>6771936</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6348,7 +6344,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6358,7 +6354,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6920,30 +6916,34 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130141107</v>
+        <v>130141064</v>
       </c>
       <c r="B60" t="n">
-        <v>91748</v>
+        <v>97791</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -6951,10 +6951,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>408453</v>
+        <v>408256</v>
       </c>
       <c r="R60" t="n">
-        <v>6771936</v>
+        <v>6771965</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6986,7 +6986,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6996,7 +6996,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8102,10 +8102,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130141037</v>
+        <v>130141070</v>
       </c>
       <c r="B71" t="n">
-        <v>91692</v>
+        <v>97791</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8113,21 +8113,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5447</v>
+        <v>221945</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8137,10 +8137,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>408048</v>
+        <v>408455</v>
       </c>
       <c r="R71" t="n">
-        <v>6772154</v>
+        <v>6771788</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8172,7 +8172,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8182,7 +8182,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8209,50 +8209,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130141055</v>
+        <v>130141037</v>
       </c>
       <c r="B72" t="n">
-        <v>57823</v>
+        <v>91692</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>408062</v>
+        <v>408048</v>
       </c>
       <c r="R72" t="n">
-        <v>6771974</v>
+        <v>6772154</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8284,7 +8279,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8294,7 +8289,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8428,45 +8423,50 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130141070</v>
+        <v>130141055</v>
       </c>
       <c r="B74" t="n">
-        <v>97791</v>
+        <v>57823</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>408455</v>
+        <v>408062</v>
       </c>
       <c r="R74" t="n">
-        <v>6771788</v>
+        <v>6771974</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8508,7 +8508,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8535,32 +8535,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130141181</v>
+        <v>130141069</v>
       </c>
       <c r="B75" t="n">
-        <v>79180</v>
+        <v>97791</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8570,10 +8570,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>408466</v>
+        <v>408016</v>
       </c>
       <c r="R75" t="n">
-        <v>6771845</v>
+        <v>6771944</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8605,7 +8605,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8615,7 +8615,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8642,32 +8642,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130141183</v>
+        <v>130141063</v>
       </c>
       <c r="B76" t="n">
-        <v>79180</v>
+        <v>97791</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8677,10 +8677,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>408441</v>
+        <v>408291</v>
       </c>
       <c r="R76" t="n">
-        <v>6771967</v>
+        <v>6771923</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8722,7 +8722,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8749,7 +8749,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>130141129</v>
+        <v>130141181</v>
       </c>
       <c r="B77" t="n">
         <v>79180</v>
@@ -8784,10 +8784,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>408199</v>
+        <v>408466</v>
       </c>
       <c r="R77" t="n">
-        <v>6771896</v>
+        <v>6771845</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8819,7 +8819,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8829,7 +8829,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8856,7 +8856,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>130141116</v>
+        <v>130141183</v>
       </c>
       <c r="B78" t="n">
         <v>79180</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>408411</v>
+        <v>408441</v>
       </c>
       <c r="R78" t="n">
-        <v>6771863</v>
+        <v>6771967</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8926,7 +8926,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8936,7 +8936,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8963,10 +8963,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>130141194</v>
+        <v>130141129</v>
       </c>
       <c r="B79" t="n">
-        <v>89124</v>
+        <v>79180</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8974,21 +8974,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8998,13 +8998,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>408303</v>
+        <v>408199</v>
       </c>
       <c r="R79" t="n">
-        <v>6771876</v>
+        <v>6771896</v>
       </c>
       <c r="S79" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9043,7 +9043,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9070,10 +9070,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>130141061</v>
+        <v>130141116</v>
       </c>
       <c r="B80" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9081,39 +9081,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>408232</v>
+        <v>408411</v>
       </c>
       <c r="R80" t="n">
-        <v>6771933</v>
+        <v>6771863</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9145,7 +9140,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9155,12 +9150,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:16</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9187,32 +9177,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>130141069</v>
+        <v>130141194</v>
       </c>
       <c r="B81" t="n">
-        <v>97791</v>
+        <v>89124</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221945</v>
+        <v>510</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9222,13 +9212,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>408016</v>
+        <v>408303</v>
       </c>
       <c r="R81" t="n">
-        <v>6771944</v>
+        <v>6771876</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9257,7 +9247,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9267,7 +9257,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9294,45 +9284,50 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>130141063</v>
+        <v>130141061</v>
       </c>
       <c r="B82" t="n">
-        <v>97791</v>
+        <v>57826</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>408291</v>
+        <v>408232</v>
       </c>
       <c r="R82" t="n">
-        <v>6771923</v>
+        <v>6771933</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9364,7 +9359,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9374,7 +9369,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9615,7 +9615,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>130141173</v>
+        <v>130141177</v>
       </c>
       <c r="B85" t="n">
         <v>79180</v>
@@ -9650,10 +9650,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>408388</v>
+        <v>408429</v>
       </c>
       <c r="R85" t="n">
-        <v>6771760</v>
+        <v>6771723</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9685,7 +9685,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9695,7 +9695,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9722,7 +9722,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>130141177</v>
+        <v>130141173</v>
       </c>
       <c r="B86" t="n">
         <v>79180</v>
@@ -9757,10 +9757,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>408429</v>
+        <v>408388</v>
       </c>
       <c r="R86" t="n">
-        <v>6771723</v>
+        <v>6771760</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9802,7 +9802,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD86" t="b">

--- a/artfynd/A 60367-2025 artfynd.xlsx
+++ b/artfynd/A 60367-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130141062</v>
+        <v>130141111</v>
       </c>
       <c r="B2" t="n">
-        <v>97791</v>
+        <v>79183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>408421</v>
+        <v>408452</v>
       </c>
       <c r="R2" t="n">
-        <v>6771953</v>
+        <v>6771936</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130141179</v>
+        <v>130141118</v>
       </c>
       <c r="B3" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>408446</v>
+        <v>408392</v>
       </c>
       <c r="R3" t="n">
-        <v>6771725</v>
+        <v>6771906</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,7 +892,7 @@
         <v>130141171</v>
       </c>
       <c r="B4" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130141191</v>
+        <v>130141179</v>
       </c>
       <c r="B5" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>408509</v>
+        <v>408446</v>
       </c>
       <c r="R5" t="n">
-        <v>6772194</v>
+        <v>6771725</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1106,7 +1106,7 @@
         <v>130141190</v>
       </c>
       <c r="B6" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130141111</v>
+        <v>130141191</v>
       </c>
       <c r="B7" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>408452</v>
+        <v>408509</v>
       </c>
       <c r="R7" t="n">
-        <v>6771936</v>
+        <v>6772194</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,32 +1317,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130141118</v>
+        <v>130141062</v>
       </c>
       <c r="B8" t="n">
-        <v>79180</v>
+        <v>97794</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>408392</v>
+        <v>408421</v>
       </c>
       <c r="R8" t="n">
-        <v>6771906</v>
+        <v>6771953</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130141045</v>
+        <v>130141134</v>
       </c>
       <c r="B9" t="n">
-        <v>91728</v>
+        <v>79183</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1435,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>408208</v>
+        <v>408063</v>
       </c>
       <c r="R9" t="n">
-        <v>6771888</v>
+        <v>6771997</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1534,7 +1534,7 @@
         <v>130141185</v>
       </c>
       <c r="B10" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>130141109</v>
       </c>
       <c r="B11" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>130141176</v>
       </c>
       <c r="B12" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130141134</v>
+        <v>130141045</v>
       </c>
       <c r="B13" t="n">
-        <v>79180</v>
+        <v>91731</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>408063</v>
+        <v>408208</v>
       </c>
       <c r="R13" t="n">
-        <v>6771997</v>
+        <v>6771888</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130141169</v>
+        <v>130141182</v>
       </c>
       <c r="B14" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>408069</v>
+        <v>408444</v>
       </c>
       <c r="R14" t="n">
-        <v>6772125</v>
+        <v>6771919</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,10 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130141133</v>
+        <v>130141169</v>
       </c>
       <c r="B15" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>408053</v>
+        <v>408069</v>
       </c>
       <c r="R15" t="n">
-        <v>6771991</v>
+        <v>6772125</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130141180</v>
+        <v>130141125</v>
       </c>
       <c r="B16" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>408470</v>
+        <v>408263</v>
       </c>
       <c r="R16" t="n">
-        <v>6771816</v>
+        <v>6771960</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,10 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130141125</v>
+        <v>130141133</v>
       </c>
       <c r="B17" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>408263</v>
+        <v>408053</v>
       </c>
       <c r="R17" t="n">
-        <v>6771960</v>
+        <v>6771991</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2387,10 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130141182</v>
+        <v>130141180</v>
       </c>
       <c r="B18" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>408444</v>
+        <v>408470</v>
       </c>
       <c r="R18" t="n">
-        <v>6771919</v>
+        <v>6771816</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2497,7 +2497,7 @@
         <v>130141068</v>
       </c>
       <c r="B19" t="n">
-        <v>97791</v>
+        <v>97794</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2601,10 +2601,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130141130</v>
+        <v>130141053</v>
       </c>
       <c r="B20" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2612,34 +2612,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>408179</v>
+        <v>408180</v>
       </c>
       <c r="R20" t="n">
-        <v>6771918</v>
+        <v>6771921</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2708,10 +2713,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130141053</v>
+        <v>130141130</v>
       </c>
       <c r="B21" t="n">
-        <v>57823</v>
+        <v>79183</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2719,39 +2724,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>408180</v>
+        <v>408179</v>
       </c>
       <c r="R21" t="n">
-        <v>6771921</v>
+        <v>6771918</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2823,7 +2823,7 @@
         <v>130141041</v>
       </c>
       <c r="B22" t="n">
-        <v>91692</v>
+        <v>91695</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>130141201</v>
       </c>
       <c r="B23" t="n">
-        <v>92385</v>
+        <v>92388</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>130141059</v>
       </c>
       <c r="B24" t="n">
-        <v>92181</v>
+        <v>92184</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3141,45 +3141,54 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130141043</v>
+        <v>130141100</v>
       </c>
       <c r="B25" t="n">
-        <v>91728</v>
+        <v>98923</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>408279</v>
+        <v>408055</v>
       </c>
       <c r="R25" t="n">
-        <v>6771971</v>
+        <v>6772067</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3211,7 +3220,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3221,7 +3230,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3248,10 +3257,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130141188</v>
+        <v>130141049</v>
       </c>
       <c r="B26" t="n">
-        <v>79180</v>
+        <v>91682</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3259,21 +3268,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3283,10 +3292,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>408452</v>
+        <v>408266</v>
       </c>
       <c r="R26" t="n">
-        <v>6772262</v>
+        <v>6771955</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3318,7 +3327,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3328,7 +3337,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3355,10 +3364,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130141114</v>
+        <v>130141188</v>
       </c>
       <c r="B27" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3390,10 +3399,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>408422</v>
+        <v>408452</v>
       </c>
       <c r="R27" t="n">
-        <v>6771930</v>
+        <v>6772262</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3425,7 +3434,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3435,7 +3444,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3462,10 +3471,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130141049</v>
+        <v>130141114</v>
       </c>
       <c r="B28" t="n">
-        <v>91679</v>
+        <v>79183</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3473,21 +3482,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3497,10 +3506,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>408266</v>
+        <v>408422</v>
       </c>
       <c r="R28" t="n">
-        <v>6771955</v>
+        <v>6771930</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3532,7 +3541,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3542,7 +3551,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3569,54 +3578,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130141100</v>
+        <v>130141043</v>
       </c>
       <c r="B29" t="n">
-        <v>98920</v>
+        <v>91731</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>408055</v>
+        <v>408279</v>
       </c>
       <c r="R29" t="n">
-        <v>6772067</v>
+        <v>6771971</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3685,10 +3685,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130141126</v>
+        <v>130141042</v>
       </c>
       <c r="B30" t="n">
-        <v>79180</v>
+        <v>91731</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3696,21 +3696,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3720,10 +3720,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>408233</v>
+        <v>408420</v>
       </c>
       <c r="R30" t="n">
-        <v>6771939</v>
+        <v>6771911</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3765,7 +3765,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3792,10 +3792,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130141122</v>
+        <v>130141178</v>
       </c>
       <c r="B31" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3827,10 +3827,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>408301</v>
+        <v>408446</v>
       </c>
       <c r="R31" t="n">
-        <v>6771872</v>
+        <v>6771720</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3899,10 +3899,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130141187</v>
+        <v>130141192</v>
       </c>
       <c r="B32" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3934,10 +3934,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>408448</v>
+        <v>408522</v>
       </c>
       <c r="R32" t="n">
-        <v>6772196</v>
+        <v>6772172</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3969,7 +3969,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4006,10 +4006,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130141192</v>
+        <v>130141122</v>
       </c>
       <c r="B33" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4041,10 +4041,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>408522</v>
+        <v>408301</v>
       </c>
       <c r="R33" t="n">
-        <v>6772172</v>
+        <v>6771872</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4113,10 +4113,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130141178</v>
+        <v>130141126</v>
       </c>
       <c r="B34" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4148,10 +4148,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>408446</v>
+        <v>408233</v>
       </c>
       <c r="R34" t="n">
-        <v>6771720</v>
+        <v>6771939</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4183,7 +4183,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4220,10 +4220,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130141042</v>
+        <v>130141187</v>
       </c>
       <c r="B35" t="n">
-        <v>91728</v>
+        <v>79183</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4231,21 +4231,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4255,10 +4255,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>408420</v>
+        <v>408448</v>
       </c>
       <c r="R35" t="n">
-        <v>6771911</v>
+        <v>6772196</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4290,7 +4290,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4300,7 +4300,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4330,7 +4330,7 @@
         <v>130141038</v>
       </c>
       <c r="B36" t="n">
-        <v>91692</v>
+        <v>91695</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
         <v>130141096</v>
       </c>
       <c r="B37" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4550,10 +4550,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130141136</v>
+        <v>130141175</v>
       </c>
       <c r="B38" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4585,10 +4585,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>408031</v>
+        <v>408404</v>
       </c>
       <c r="R38" t="n">
-        <v>6772025</v>
+        <v>6771749</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4620,7 +4620,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4630,7 +4630,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4657,10 +4657,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130141175</v>
+        <v>130141136</v>
       </c>
       <c r="B39" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4692,10 +4692,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>408404</v>
+        <v>408031</v>
       </c>
       <c r="R39" t="n">
-        <v>6771749</v>
+        <v>6772025</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4727,7 +4727,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4764,10 +4764,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130141113</v>
+        <v>130141052</v>
       </c>
       <c r="B40" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4775,34 +4775,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>408416</v>
+        <v>408232</v>
       </c>
       <c r="R40" t="n">
-        <v>6771941</v>
+        <v>6771944</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4834,7 +4839,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4844,7 +4849,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4871,10 +4876,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130141052</v>
+        <v>130141108</v>
       </c>
       <c r="B41" t="n">
-        <v>57823</v>
+        <v>91751</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4882,39 +4887,30 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>408232</v>
+        <v>408452</v>
       </c>
       <c r="R41" t="n">
-        <v>6771944</v>
+        <v>6771915</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4946,7 +4942,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4956,7 +4952,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4983,54 +4979,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130141101</v>
+        <v>130141113</v>
       </c>
       <c r="B42" t="n">
-        <v>98920</v>
+        <v>79183</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>408032</v>
+        <v>408416</v>
       </c>
       <c r="R42" t="n">
-        <v>6772075</v>
+        <v>6771941</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5062,7 +5049,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5072,7 +5059,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5099,41 +5086,54 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130141108</v>
+        <v>130141101</v>
       </c>
       <c r="B43" t="n">
-        <v>91748</v>
+        <v>98923</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>408452</v>
+        <v>408032</v>
       </c>
       <c r="R43" t="n">
-        <v>6771915</v>
+        <v>6772075</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5165,7 +5165,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5175,7 +5175,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5317,7 +5317,7 @@
         <v>130141060</v>
       </c>
       <c r="B45" t="n">
-        <v>92181</v>
+        <v>92184</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5421,10 +5421,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130141105</v>
+        <v>130141128</v>
       </c>
       <c r="B46" t="n">
-        <v>91742</v>
+        <v>79183</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5432,21 +5432,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5456,10 +5456,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>408032</v>
+        <v>408213</v>
       </c>
       <c r="R46" t="n">
-        <v>6772075</v>
+        <v>6771880</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5491,7 +5491,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5528,32 +5528,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130141073</v>
+        <v>130141184</v>
       </c>
       <c r="B47" t="n">
-        <v>80313</v>
+        <v>79183</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5563,10 +5563,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>408029</v>
+        <v>408448</v>
       </c>
       <c r="R47" t="n">
-        <v>6771956</v>
+        <v>6771990</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5608,7 +5608,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5635,10 +5635,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130141184</v>
+        <v>130141123</v>
       </c>
       <c r="B48" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5670,10 +5670,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>408448</v>
+        <v>408291</v>
       </c>
       <c r="R48" t="n">
-        <v>6771990</v>
+        <v>6771913</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5705,7 +5705,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5715,7 +5715,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5742,10 +5742,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130141123</v>
+        <v>130141120</v>
       </c>
       <c r="B49" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5777,10 +5777,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>408291</v>
+        <v>408363</v>
       </c>
       <c r="R49" t="n">
-        <v>6771913</v>
+        <v>6771889</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5812,7 +5812,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5822,7 +5822,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5849,32 +5849,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130141128</v>
+        <v>130141073</v>
       </c>
       <c r="B50" t="n">
-        <v>79180</v>
+        <v>80316</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5884,10 +5884,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>408213</v>
+        <v>408029</v>
       </c>
       <c r="R50" t="n">
-        <v>6771880</v>
+        <v>6771956</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5919,7 +5919,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5929,7 +5929,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5956,10 +5956,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130141120</v>
+        <v>130141105</v>
       </c>
       <c r="B51" t="n">
-        <v>79180</v>
+        <v>91745</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5967,21 +5967,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5991,10 +5991,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>408363</v>
+        <v>408032</v>
       </c>
       <c r="R51" t="n">
-        <v>6771889</v>
+        <v>6772075</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6036,7 +6036,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6066,7 +6066,7 @@
         <v>130141103</v>
       </c>
       <c r="B52" t="n">
-        <v>80251</v>
+        <v>80254</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         <v>130141196</v>
       </c>
       <c r="B53" t="n">
-        <v>89124</v>
+        <v>89125</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6278,30 +6278,34 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130141107</v>
+        <v>130141064</v>
       </c>
       <c r="B54" t="n">
-        <v>91748</v>
+        <v>97794</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6309,10 +6313,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>408453</v>
+        <v>408256</v>
       </c>
       <c r="R54" t="n">
-        <v>6771936</v>
+        <v>6771965</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6344,7 +6348,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6354,7 +6358,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6384,7 +6388,7 @@
         <v>130141189</v>
       </c>
       <c r="B55" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6488,10 +6492,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130141137</v>
+        <v>130141135</v>
       </c>
       <c r="B56" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6523,10 +6527,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>408034</v>
+        <v>408031</v>
       </c>
       <c r="R56" t="n">
-        <v>6772034</v>
+        <v>6772014</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6558,7 +6562,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6568,7 +6572,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6598,7 +6602,7 @@
         <v>130141115</v>
       </c>
       <c r="B57" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6702,10 +6706,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130141135</v>
+        <v>130141117</v>
       </c>
       <c r="B58" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6737,10 +6741,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>408031</v>
+        <v>408409</v>
       </c>
       <c r="R58" t="n">
-        <v>6772014</v>
+        <v>6771881</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6772,7 +6776,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6782,7 +6786,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6809,10 +6813,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130141117</v>
+        <v>130141137</v>
       </c>
       <c r="B59" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6844,10 +6848,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>408409</v>
+        <v>408034</v>
       </c>
       <c r="R59" t="n">
-        <v>6771881</v>
+        <v>6772034</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6879,7 +6883,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6889,7 +6893,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6916,34 +6920,30 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130141064</v>
+        <v>130141107</v>
       </c>
       <c r="B60" t="n">
-        <v>97791</v>
+        <v>91751</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -6951,10 +6951,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>408256</v>
+        <v>408453</v>
       </c>
       <c r="R60" t="n">
-        <v>6771965</v>
+        <v>6771936</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6986,7 +6986,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6996,7 +6996,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7023,32 +7023,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130141195</v>
+        <v>130141040</v>
       </c>
       <c r="B61" t="n">
-        <v>89124</v>
+        <v>91695</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>510</v>
+        <v>5447</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7058,10 +7058,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>408282</v>
+        <v>408073</v>
       </c>
       <c r="R61" t="n">
-        <v>6771935</v>
+        <v>6772016</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7093,7 +7093,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7103,7 +7103,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7130,32 +7130,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130141035</v>
+        <v>130141174</v>
       </c>
       <c r="B62" t="n">
-        <v>91692</v>
+        <v>79183</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7165,10 +7165,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>408053</v>
+        <v>408396</v>
       </c>
       <c r="R62" t="n">
-        <v>6772152</v>
+        <v>6771759</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7210,7 +7210,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7237,10 +7237,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130141040</v>
+        <v>130141035</v>
       </c>
       <c r="B63" t="n">
-        <v>91692</v>
+        <v>91695</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7272,10 +7272,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>408073</v>
+        <v>408053</v>
       </c>
       <c r="R63" t="n">
-        <v>6772016</v>
+        <v>6772152</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7307,7 +7307,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7344,10 +7344,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130141174</v>
+        <v>130141195</v>
       </c>
       <c r="B64" t="n">
-        <v>79180</v>
+        <v>89125</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7355,21 +7355,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7379,10 +7379,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>408396</v>
+        <v>408282</v>
       </c>
       <c r="R64" t="n">
-        <v>6771759</v>
+        <v>6771935</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7414,7 +7414,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7424,7 +7424,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7451,32 +7451,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130141071</v>
+        <v>130141168</v>
       </c>
       <c r="B65" t="n">
-        <v>97791</v>
+        <v>79183</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7486,10 +7486,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>408448</v>
+        <v>408044</v>
       </c>
       <c r="R65" t="n">
-        <v>6771891</v>
+        <v>6772152</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7521,7 +7521,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7558,32 +7558,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130141168</v>
+        <v>130141071</v>
       </c>
       <c r="B66" t="n">
-        <v>79180</v>
+        <v>97794</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7593,10 +7593,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>408044</v>
+        <v>408448</v>
       </c>
       <c r="R66" t="n">
-        <v>6772152</v>
+        <v>6771891</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7628,7 +7628,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7638,7 +7638,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7668,7 +7668,7 @@
         <v>130141098</v>
       </c>
       <c r="B67" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7781,10 +7781,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130141119</v>
+        <v>130141138</v>
       </c>
       <c r="B68" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7816,10 +7816,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>408380</v>
+        <v>408043</v>
       </c>
       <c r="R68" t="n">
-        <v>6771903</v>
+        <v>6772111</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7851,7 +7851,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7861,7 +7861,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7888,10 +7888,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130141138</v>
+        <v>130141112</v>
       </c>
       <c r="B69" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7923,10 +7923,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>408043</v>
+        <v>408432</v>
       </c>
       <c r="R69" t="n">
-        <v>6772111</v>
+        <v>6771948</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7958,7 +7958,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7968,7 +7968,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7995,10 +7995,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130141112</v>
+        <v>130141119</v>
       </c>
       <c r="B70" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8030,10 +8030,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>408432</v>
+        <v>408380</v>
       </c>
       <c r="R70" t="n">
-        <v>6771948</v>
+        <v>6771903</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8065,7 +8065,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8102,32 +8102,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130141070</v>
+        <v>130141048</v>
       </c>
       <c r="B71" t="n">
-        <v>97791</v>
+        <v>91731</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8137,10 +8137,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>408455</v>
+        <v>408067</v>
       </c>
       <c r="R71" t="n">
-        <v>6771788</v>
+        <v>6772051</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8172,7 +8172,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8182,7 +8182,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8212,7 +8212,7 @@
         <v>130141037</v>
       </c>
       <c r="B72" t="n">
-        <v>91692</v>
+        <v>91695</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8316,10 +8316,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130141048</v>
+        <v>130141055</v>
       </c>
       <c r="B73" t="n">
-        <v>91728</v>
+        <v>57823</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8327,34 +8327,39 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>408067</v>
+        <v>408062</v>
       </c>
       <c r="R73" t="n">
-        <v>6772051</v>
+        <v>6771974</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8386,7 +8391,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8396,7 +8401,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8423,50 +8428,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130141055</v>
+        <v>130141070</v>
       </c>
       <c r="B74" t="n">
-        <v>57823</v>
+        <v>97794</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>408062</v>
+        <v>408455</v>
       </c>
       <c r="R74" t="n">
-        <v>6771974</v>
+        <v>6771788</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8508,7 +8508,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8538,7 +8538,7 @@
         <v>130141069</v>
       </c>
       <c r="B75" t="n">
-        <v>97791</v>
+        <v>97794</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8645,7 +8645,7 @@
         <v>130141063</v>
       </c>
       <c r="B76" t="n">
-        <v>97791</v>
+        <v>97794</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>130141181</v>
       </c>
       <c r="B77" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8856,10 +8856,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>130141183</v>
+        <v>130141129</v>
       </c>
       <c r="B78" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>408441</v>
+        <v>408199</v>
       </c>
       <c r="R78" t="n">
-        <v>6771967</v>
+        <v>6771896</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8926,7 +8926,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8936,7 +8936,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8963,10 +8963,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>130141129</v>
+        <v>130141116</v>
       </c>
       <c r="B79" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8998,10 +8998,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>408199</v>
+        <v>408411</v>
       </c>
       <c r="R79" t="n">
-        <v>6771896</v>
+        <v>6771863</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9033,7 +9033,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9043,7 +9043,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9070,10 +9070,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>130141116</v>
+        <v>130141183</v>
       </c>
       <c r="B80" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9105,10 +9105,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>408411</v>
+        <v>408441</v>
       </c>
       <c r="R80" t="n">
-        <v>6771863</v>
+        <v>6771967</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9140,7 +9140,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9150,7 +9150,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9177,10 +9177,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>130141194</v>
+        <v>130141061</v>
       </c>
       <c r="B81" t="n">
-        <v>89124</v>
+        <v>57826</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9188,37 +9188,42 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>408303</v>
+        <v>408232</v>
       </c>
       <c r="R81" t="n">
-        <v>6771876</v>
+        <v>6771933</v>
       </c>
       <c r="S81" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9247,7 +9252,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9257,7 +9262,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9284,10 +9294,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>130141061</v>
+        <v>130141194</v>
       </c>
       <c r="B82" t="n">
-        <v>57826</v>
+        <v>89125</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9295,42 +9305,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>408232</v>
+        <v>408303</v>
       </c>
       <c r="R82" t="n">
-        <v>6771933</v>
+        <v>6771876</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9359,7 +9364,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9369,12 +9374,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:16</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9404,7 +9404,7 @@
         <v>130141186</v>
       </c>
       <c r="B83" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9508,45 +9508,54 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>130141170</v>
+        <v>130141094</v>
       </c>
       <c r="B84" t="n">
-        <v>79180</v>
+        <v>98923</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>408080</v>
+        <v>408187</v>
       </c>
       <c r="R84" t="n">
-        <v>6772000</v>
+        <v>6771901</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9578,7 +9587,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9588,7 +9597,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9615,10 +9624,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>130141177</v>
+        <v>130141124</v>
       </c>
       <c r="B85" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9650,10 +9659,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>408429</v>
+        <v>408276</v>
       </c>
       <c r="R85" t="n">
-        <v>6771723</v>
+        <v>6771996</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9685,7 +9694,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9695,7 +9704,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9722,10 +9731,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>130141173</v>
+        <v>130141131</v>
       </c>
       <c r="B86" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9757,10 +9766,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>408388</v>
+        <v>408169</v>
       </c>
       <c r="R86" t="n">
-        <v>6771760</v>
+        <v>6771937</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9792,7 +9801,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9802,7 +9811,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9829,10 +9838,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>130141110</v>
+        <v>130141173</v>
       </c>
       <c r="B87" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9864,10 +9873,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>408466</v>
+        <v>408388</v>
       </c>
       <c r="R87" t="n">
-        <v>6771924</v>
+        <v>6771760</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9899,7 +9908,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9909,7 +9918,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9936,10 +9945,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>130141131</v>
+        <v>130141177</v>
       </c>
       <c r="B88" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9971,10 +9980,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>408169</v>
+        <v>408429</v>
       </c>
       <c r="R88" t="n">
-        <v>6771937</v>
+        <v>6771723</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10006,7 +10015,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10016,7 +10025,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10043,10 +10052,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>130141124</v>
+        <v>130141170</v>
       </c>
       <c r="B89" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10078,10 +10087,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>408276</v>
+        <v>408080</v>
       </c>
       <c r="R89" t="n">
-        <v>6771996</v>
+        <v>6772000</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10113,7 +10122,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10123,7 +10132,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10150,54 +10159,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>130141094</v>
+        <v>130141110</v>
       </c>
       <c r="B90" t="n">
-        <v>98920</v>
+        <v>79183</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>408187</v>
+        <v>408466</v>
       </c>
       <c r="R90" t="n">
-        <v>6771901</v>
+        <v>6771924</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10229,7 +10229,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10239,7 +10239,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD90" t="b">

--- a/artfynd/A 60367-2025 artfynd.xlsx
+++ b/artfynd/A 60367-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130141111</v>
+        <v>130141062</v>
       </c>
       <c r="B2" t="n">
-        <v>79183</v>
+        <v>97820</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>408452</v>
+        <v>408421</v>
       </c>
       <c r="R2" t="n">
-        <v>6771936</v>
+        <v>6771953</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130141118</v>
+        <v>130141111</v>
       </c>
       <c r="B3" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>408392</v>
+        <v>408452</v>
       </c>
       <c r="R3" t="n">
-        <v>6771906</v>
+        <v>6771936</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130141171</v>
+        <v>130141118</v>
       </c>
       <c r="B4" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>408023</v>
+        <v>408392</v>
       </c>
       <c r="R4" t="n">
-        <v>6771952</v>
+        <v>6771906</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130141179</v>
+        <v>130141171</v>
       </c>
       <c r="B5" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>408446</v>
+        <v>408023</v>
       </c>
       <c r="R5" t="n">
-        <v>6771725</v>
+        <v>6771952</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130141190</v>
+        <v>130141179</v>
       </c>
       <c r="B6" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>408513</v>
+        <v>408446</v>
       </c>
       <c r="R6" t="n">
-        <v>6772199</v>
+        <v>6771725</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130141191</v>
+        <v>130141190</v>
       </c>
       <c r="B7" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>408509</v>
+        <v>408513</v>
       </c>
       <c r="R7" t="n">
-        <v>6772194</v>
+        <v>6772199</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,32 +1317,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130141062</v>
+        <v>130141191</v>
       </c>
       <c r="B8" t="n">
-        <v>97794</v>
+        <v>79209</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>408421</v>
+        <v>408509</v>
       </c>
       <c r="R8" t="n">
-        <v>6771953</v>
+        <v>6772194</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130141134</v>
+        <v>130141045</v>
       </c>
       <c r="B9" t="n">
-        <v>79183</v>
+        <v>91757</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1435,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>408063</v>
+        <v>408208</v>
       </c>
       <c r="R9" t="n">
-        <v>6771997</v>
+        <v>6771888</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130141185</v>
+        <v>130141134</v>
       </c>
       <c r="B10" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>408470</v>
+        <v>408063</v>
       </c>
       <c r="R10" t="n">
-        <v>6772171</v>
+        <v>6771997</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130141109</v>
+        <v>130141185</v>
       </c>
       <c r="B11" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>408039</v>
+        <v>408470</v>
       </c>
       <c r="R11" t="n">
-        <v>6771959</v>
+        <v>6772171</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130141176</v>
+        <v>130141109</v>
       </c>
       <c r="B12" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>408421</v>
+        <v>408039</v>
       </c>
       <c r="R12" t="n">
-        <v>6771727</v>
+        <v>6771959</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130141045</v>
+        <v>130141176</v>
       </c>
       <c r="B13" t="n">
-        <v>91731</v>
+        <v>79209</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>408208</v>
+        <v>408421</v>
       </c>
       <c r="R13" t="n">
-        <v>6771888</v>
+        <v>6771727</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1962,7 +1962,7 @@
         <v>130141182</v>
       </c>
       <c r="B14" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>130141169</v>
       </c>
       <c r="B15" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>130141125</v>
       </c>
       <c r="B16" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>130141133</v>
       </c>
       <c r="B17" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>130141180</v>
       </c>
       <c r="B18" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>130141068</v>
       </c>
       <c r="B19" t="n">
-        <v>97794</v>
+        <v>97820</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2601,50 +2601,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130141053</v>
+        <v>130141201</v>
       </c>
       <c r="B20" t="n">
-        <v>57823</v>
+        <v>92414</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>1965</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Citronporing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Antrodiella citrinella</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä &amp; Ryvarden</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>408180</v>
+        <v>408238</v>
       </c>
       <c r="R20" t="n">
-        <v>6771921</v>
+        <v>6771897</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2676,7 +2671,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2686,7 +2681,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2713,32 +2708,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130141130</v>
+        <v>130141059</v>
       </c>
       <c r="B21" t="n">
-        <v>79183</v>
+        <v>92210</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2748,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>408179</v>
+        <v>408213</v>
       </c>
       <c r="R21" t="n">
-        <v>6771918</v>
+        <v>6771880</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2783,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2793,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2820,32 +2815,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130141041</v>
+        <v>130141130</v>
       </c>
       <c r="B22" t="n">
-        <v>91695</v>
+        <v>79209</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2855,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>408520</v>
+        <v>408179</v>
       </c>
       <c r="R22" t="n">
-        <v>6772210</v>
+        <v>6771918</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2890,7 +2885,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2900,7 +2895,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2927,32 +2922,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130141201</v>
+        <v>130141041</v>
       </c>
       <c r="B23" t="n">
-        <v>92388</v>
+        <v>91721</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1965</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Citronporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Antrodiella citrinella</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Ryvarden</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2962,10 +2957,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>408238</v>
+        <v>408520</v>
       </c>
       <c r="R23" t="n">
-        <v>6771897</v>
+        <v>6772210</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2997,7 +2992,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3007,7 +3002,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3034,45 +3029,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130141059</v>
+        <v>130141053</v>
       </c>
       <c r="B24" t="n">
-        <v>92184</v>
+        <v>57849</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>408213</v>
+        <v>408180</v>
       </c>
       <c r="R24" t="n">
-        <v>6771880</v>
+        <v>6771921</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3104,7 +3104,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3141,54 +3141,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130141100</v>
+        <v>130141043</v>
       </c>
       <c r="B25" t="n">
-        <v>98923</v>
+        <v>91757</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>408055</v>
+        <v>408279</v>
       </c>
       <c r="R25" t="n">
-        <v>6772067</v>
+        <v>6771971</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3220,7 +3211,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3230,7 +3221,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3257,10 +3248,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130141049</v>
+        <v>130141114</v>
       </c>
       <c r="B26" t="n">
-        <v>91682</v>
+        <v>79209</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3268,21 +3259,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3292,10 +3283,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>408266</v>
+        <v>408422</v>
       </c>
       <c r="R26" t="n">
-        <v>6771955</v>
+        <v>6771930</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3327,7 +3318,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3337,7 +3328,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3364,45 +3355,54 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130141188</v>
+        <v>130141100</v>
       </c>
       <c r="B27" t="n">
-        <v>79183</v>
+        <v>98949</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>408452</v>
+        <v>408055</v>
       </c>
       <c r="R27" t="n">
-        <v>6772262</v>
+        <v>6772067</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3471,10 +3471,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130141114</v>
+        <v>130141049</v>
       </c>
       <c r="B28" t="n">
-        <v>79183</v>
+        <v>91708</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3482,21 +3482,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3506,10 +3506,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>408422</v>
+        <v>408266</v>
       </c>
       <c r="R28" t="n">
-        <v>6771930</v>
+        <v>6771955</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3578,10 +3578,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130141043</v>
+        <v>130141188</v>
       </c>
       <c r="B29" t="n">
-        <v>91731</v>
+        <v>79209</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3589,21 +3589,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>408279</v>
+        <v>408452</v>
       </c>
       <c r="R29" t="n">
-        <v>6771971</v>
+        <v>6772262</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3688,7 +3688,7 @@
         <v>130141042</v>
       </c>
       <c r="B30" t="n">
-        <v>91731</v>
+        <v>91757</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3792,10 +3792,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130141178</v>
+        <v>130141122</v>
       </c>
       <c r="B31" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3827,10 +3827,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>408446</v>
+        <v>408301</v>
       </c>
       <c r="R31" t="n">
-        <v>6771720</v>
+        <v>6771872</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3899,10 +3899,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130141192</v>
+        <v>130141178</v>
       </c>
       <c r="B32" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3934,10 +3934,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>408522</v>
+        <v>408446</v>
       </c>
       <c r="R32" t="n">
-        <v>6772172</v>
+        <v>6771720</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3969,7 +3969,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4006,10 +4006,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130141122</v>
+        <v>130141192</v>
       </c>
       <c r="B33" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4041,10 +4041,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>408301</v>
+        <v>408522</v>
       </c>
       <c r="R33" t="n">
-        <v>6771872</v>
+        <v>6772172</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4116,7 +4116,7 @@
         <v>130141126</v>
       </c>
       <c r="B34" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         <v>130141187</v>
       </c>
       <c r="B35" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4327,45 +4327,54 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130141038</v>
+        <v>130141096</v>
       </c>
       <c r="B36" t="n">
-        <v>91695</v>
+        <v>98949</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>408067</v>
+        <v>408022</v>
       </c>
       <c r="R36" t="n">
-        <v>6772053</v>
+        <v>6772065</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4397,7 +4406,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4407,7 +4416,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4434,54 +4443,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130141096</v>
+        <v>130141038</v>
       </c>
       <c r="B37" t="n">
-        <v>98923</v>
+        <v>91721</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>408022</v>
+        <v>408067</v>
       </c>
       <c r="R37" t="n">
-        <v>6772065</v>
+        <v>6772053</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4513,7 +4513,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4523,7 +4523,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4553,7 +4553,7 @@
         <v>130141175</v>
       </c>
       <c r="B38" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         <v>130141136</v>
       </c>
       <c r="B39" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4764,10 +4764,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130141052</v>
+        <v>130141108</v>
       </c>
       <c r="B40" t="n">
-        <v>57823</v>
+        <v>91777</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4775,39 +4775,30 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>408232</v>
+        <v>408452</v>
       </c>
       <c r="R40" t="n">
-        <v>6771944</v>
+        <v>6771915</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4839,7 +4830,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4849,7 +4840,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4876,10 +4867,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130141108</v>
+        <v>130141113</v>
       </c>
       <c r="B41" t="n">
-        <v>91751</v>
+        <v>79209</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4887,19 +4878,23 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4907,10 +4902,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>408452</v>
+        <v>408416</v>
       </c>
       <c r="R41" t="n">
-        <v>6771915</v>
+        <v>6771941</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4942,7 +4937,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4952,7 +4947,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4979,10 +4974,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130141113</v>
+        <v>130141052</v>
       </c>
       <c r="B42" t="n">
-        <v>79183</v>
+        <v>57849</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4990,34 +4985,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>408416</v>
+        <v>408232</v>
       </c>
       <c r="R42" t="n">
-        <v>6771941</v>
+        <v>6771944</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5049,7 +5049,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5059,7 +5059,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5089,7 +5089,7 @@
         <v>130141101</v>
       </c>
       <c r="B43" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5202,50 +5202,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130141029</v>
+        <v>130141060</v>
       </c>
       <c r="B44" t="n">
-        <v>5197</v>
+        <v>92210</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>105930</v>
+        <v>1209</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>408243</v>
+        <v>408215</v>
       </c>
       <c r="R44" t="n">
-        <v>6771879</v>
+        <v>6771888</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5277,7 +5272,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5287,7 +5282,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5314,45 +5309,50 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130141060</v>
+        <v>130141029</v>
       </c>
       <c r="B45" t="n">
-        <v>92184</v>
+        <v>5197</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1209</v>
+        <v>105930</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>408215</v>
+        <v>408243</v>
       </c>
       <c r="R45" t="n">
-        <v>6771888</v>
+        <v>6771879</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5384,7 +5384,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5394,7 +5394,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5421,32 +5421,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130141128</v>
+        <v>130141103</v>
       </c>
       <c r="B46" t="n">
-        <v>79183</v>
+        <v>80280</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>229748</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5456,10 +5456,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>408213</v>
+        <v>408441</v>
       </c>
       <c r="R46" t="n">
-        <v>6771880</v>
+        <v>6771723</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5491,7 +5491,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5510,6 +5510,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5528,10 +5529,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130141184</v>
+        <v>130141105</v>
       </c>
       <c r="B47" t="n">
-        <v>79183</v>
+        <v>91771</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5539,21 +5540,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5563,10 +5564,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>408448</v>
+        <v>408032</v>
       </c>
       <c r="R47" t="n">
-        <v>6771990</v>
+        <v>6772075</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5598,7 +5599,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5608,7 +5609,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5635,32 +5636,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130141123</v>
+        <v>130141073</v>
       </c>
       <c r="B48" t="n">
-        <v>79183</v>
+        <v>80342</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5670,10 +5671,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>408291</v>
+        <v>408029</v>
       </c>
       <c r="R48" t="n">
-        <v>6771913</v>
+        <v>6771956</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5705,7 +5706,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5715,7 +5716,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5742,10 +5743,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130141120</v>
+        <v>130141128</v>
       </c>
       <c r="B49" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5777,10 +5778,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>408363</v>
+        <v>408213</v>
       </c>
       <c r="R49" t="n">
-        <v>6771889</v>
+        <v>6771880</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5812,7 +5813,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5822,7 +5823,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5849,32 +5850,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130141073</v>
+        <v>130141184</v>
       </c>
       <c r="B50" t="n">
-        <v>80316</v>
+        <v>79209</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5884,10 +5885,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>408029</v>
+        <v>408448</v>
       </c>
       <c r="R50" t="n">
-        <v>6771956</v>
+        <v>6771990</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5919,7 +5920,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5929,7 +5930,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5956,10 +5957,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130141105</v>
+        <v>130141123</v>
       </c>
       <c r="B51" t="n">
-        <v>91745</v>
+        <v>79209</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5967,21 +5968,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5991,10 +5992,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>408032</v>
+        <v>408291</v>
       </c>
       <c r="R51" t="n">
-        <v>6772075</v>
+        <v>6771913</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6026,7 +6027,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6036,7 +6037,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6063,32 +6064,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130141103</v>
+        <v>130141120</v>
       </c>
       <c r="B52" t="n">
-        <v>80254</v>
+        <v>79209</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>229748</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6098,10 +6099,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>408441</v>
+        <v>408363</v>
       </c>
       <c r="R52" t="n">
-        <v>6771723</v>
+        <v>6771889</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6133,7 +6134,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6143,7 +6144,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6152,7 +6153,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6174,7 +6174,7 @@
         <v>130141196</v>
       </c>
       <c r="B53" t="n">
-        <v>89125</v>
+        <v>89151</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6278,32 +6278,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130141064</v>
+        <v>130141137</v>
       </c>
       <c r="B54" t="n">
-        <v>97794</v>
+        <v>79209</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6313,10 +6313,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>408256</v>
+        <v>408034</v>
       </c>
       <c r="R54" t="n">
-        <v>6771965</v>
+        <v>6772034</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6348,7 +6348,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6358,7 +6358,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6385,10 +6385,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130141189</v>
+        <v>130141107</v>
       </c>
       <c r="B55" t="n">
-        <v>79183</v>
+        <v>91777</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6396,23 +6396,19 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6420,10 +6416,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>408512</v>
+        <v>408453</v>
       </c>
       <c r="R55" t="n">
-        <v>6772218</v>
+        <v>6771936</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6455,7 +6451,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6465,7 +6461,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6492,10 +6488,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130141135</v>
+        <v>130141189</v>
       </c>
       <c r="B56" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6527,10 +6523,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>408031</v>
+        <v>408512</v>
       </c>
       <c r="R56" t="n">
-        <v>6772014</v>
+        <v>6772218</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6562,7 +6558,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6572,7 +6568,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6599,10 +6595,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130141115</v>
+        <v>130141135</v>
       </c>
       <c r="B57" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6634,10 +6630,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>408423</v>
+        <v>408031</v>
       </c>
       <c r="R57" t="n">
-        <v>6771906</v>
+        <v>6772014</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6669,7 +6665,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6679,7 +6675,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6706,10 +6702,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130141117</v>
+        <v>130141115</v>
       </c>
       <c r="B58" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6741,10 +6737,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>408409</v>
+        <v>408423</v>
       </c>
       <c r="R58" t="n">
-        <v>6771881</v>
+        <v>6771906</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6776,7 +6772,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6786,7 +6782,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6813,10 +6809,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130141137</v>
+        <v>130141117</v>
       </c>
       <c r="B59" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6848,10 +6844,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>408034</v>
+        <v>408409</v>
       </c>
       <c r="R59" t="n">
-        <v>6772034</v>
+        <v>6771881</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6883,7 +6879,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6893,7 +6889,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6920,30 +6916,34 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130141107</v>
+        <v>130141064</v>
       </c>
       <c r="B60" t="n">
-        <v>91751</v>
+        <v>97820</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -6951,10 +6951,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>408453</v>
+        <v>408256</v>
       </c>
       <c r="R60" t="n">
-        <v>6771936</v>
+        <v>6771965</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6986,7 +6986,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6996,7 +6996,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7026,7 +7026,7 @@
         <v>130141040</v>
       </c>
       <c r="B61" t="n">
-        <v>91695</v>
+        <v>91721</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7130,32 +7130,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130141174</v>
+        <v>130141035</v>
       </c>
       <c r="B62" t="n">
-        <v>79183</v>
+        <v>91721</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7165,10 +7165,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>408396</v>
+        <v>408053</v>
       </c>
       <c r="R62" t="n">
-        <v>6771759</v>
+        <v>6772152</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7210,7 +7210,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7237,32 +7237,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130141035</v>
+        <v>130141174</v>
       </c>
       <c r="B63" t="n">
-        <v>91695</v>
+        <v>79209</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7272,10 +7272,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>408053</v>
+        <v>408396</v>
       </c>
       <c r="R63" t="n">
-        <v>6772152</v>
+        <v>6771759</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7307,7 +7307,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7347,7 +7347,7 @@
         <v>130141195</v>
       </c>
       <c r="B64" t="n">
-        <v>89125</v>
+        <v>89151</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7454,7 +7454,7 @@
         <v>130141168</v>
       </c>
       <c r="B65" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7561,7 +7561,7 @@
         <v>130141071</v>
       </c>
       <c r="B66" t="n">
-        <v>97794</v>
+        <v>97820</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7668,7 +7668,7 @@
         <v>130141098</v>
       </c>
       <c r="B67" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7784,7 +7784,7 @@
         <v>130141138</v>
       </c>
       <c r="B68" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         <v>130141112</v>
       </c>
       <c r="B69" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7998,7 +7998,7 @@
         <v>130141119</v>
       </c>
       <c r="B70" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8102,10 +8102,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130141048</v>
+        <v>130141055</v>
       </c>
       <c r="B71" t="n">
-        <v>91731</v>
+        <v>57849</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8113,34 +8113,39 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>408067</v>
+        <v>408062</v>
       </c>
       <c r="R71" t="n">
-        <v>6772051</v>
+        <v>6771974</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8172,7 +8177,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8182,7 +8187,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8209,32 +8214,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130141037</v>
+        <v>130141048</v>
       </c>
       <c r="B72" t="n">
-        <v>91695</v>
+        <v>91757</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8244,10 +8249,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>408048</v>
+        <v>408067</v>
       </c>
       <c r="R72" t="n">
-        <v>6772154</v>
+        <v>6772051</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8279,7 +8284,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8289,7 +8294,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8316,50 +8321,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130141055</v>
+        <v>130141037</v>
       </c>
       <c r="B73" t="n">
-        <v>57823</v>
+        <v>91721</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>408062</v>
+        <v>408048</v>
       </c>
       <c r="R73" t="n">
-        <v>6771974</v>
+        <v>6772154</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8391,7 +8391,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8401,7 +8401,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8431,7 +8431,7 @@
         <v>130141070</v>
       </c>
       <c r="B74" t="n">
-        <v>97794</v>
+        <v>97820</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8535,32 +8535,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130141069</v>
+        <v>130141183</v>
       </c>
       <c r="B75" t="n">
-        <v>97794</v>
+        <v>79209</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8570,10 +8570,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>408016</v>
+        <v>408441</v>
       </c>
       <c r="R75" t="n">
-        <v>6771944</v>
+        <v>6771967</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8605,7 +8605,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8615,7 +8615,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8642,32 +8642,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130141063</v>
+        <v>130141181</v>
       </c>
       <c r="B76" t="n">
-        <v>97794</v>
+        <v>79209</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8677,10 +8677,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>408291</v>
+        <v>408466</v>
       </c>
       <c r="R76" t="n">
-        <v>6771923</v>
+        <v>6771845</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8722,7 +8722,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8749,10 +8749,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>130141181</v>
+        <v>130141116</v>
       </c>
       <c r="B77" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8784,10 +8784,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>408466</v>
+        <v>408411</v>
       </c>
       <c r="R77" t="n">
-        <v>6771845</v>
+        <v>6771863</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8819,7 +8819,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8829,7 +8829,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8856,10 +8856,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>130141129</v>
+        <v>130141194</v>
       </c>
       <c r="B78" t="n">
-        <v>79183</v>
+        <v>89151</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8867,21 +8867,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8891,13 +8891,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>408199</v>
+        <v>408303</v>
       </c>
       <c r="R78" t="n">
-        <v>6771896</v>
+        <v>6771876</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8926,7 +8926,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8936,7 +8936,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8963,10 +8963,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>130141116</v>
+        <v>130141129</v>
       </c>
       <c r="B79" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8998,10 +8998,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>408411</v>
+        <v>408199</v>
       </c>
       <c r="R79" t="n">
-        <v>6771863</v>
+        <v>6771896</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9033,7 +9033,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9043,7 +9043,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9070,10 +9070,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>130141183</v>
+        <v>130141061</v>
       </c>
       <c r="B80" t="n">
-        <v>79183</v>
+        <v>57852</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9081,34 +9081,39 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>408441</v>
+        <v>408232</v>
       </c>
       <c r="R80" t="n">
-        <v>6771967</v>
+        <v>6771933</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9140,7 +9145,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9150,7 +9155,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9177,50 +9187,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>130141061</v>
+        <v>130141069</v>
       </c>
       <c r="B81" t="n">
-        <v>57826</v>
+        <v>97820</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>408232</v>
+        <v>408016</v>
       </c>
       <c r="R81" t="n">
-        <v>6771933</v>
+        <v>6771944</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9252,7 +9257,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9262,12 +9267,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>11:16</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9294,32 +9294,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>130141194</v>
+        <v>130141063</v>
       </c>
       <c r="B82" t="n">
-        <v>89125</v>
+        <v>97820</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>510</v>
+        <v>221945</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9329,13 +9329,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>408303</v>
+        <v>408291</v>
       </c>
       <c r="R82" t="n">
-        <v>6771876</v>
+        <v>6771923</v>
       </c>
       <c r="S82" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9364,7 +9364,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9374,7 +9374,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9404,7 +9404,7 @@
         <v>130141186</v>
       </c>
       <c r="B83" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9508,54 +9508,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>130141094</v>
+        <v>130141173</v>
       </c>
       <c r="B84" t="n">
-        <v>98923</v>
+        <v>79209</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>408187</v>
+        <v>408388</v>
       </c>
       <c r="R84" t="n">
-        <v>6771901</v>
+        <v>6771760</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9587,7 +9578,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9597,7 +9588,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9624,10 +9615,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>130141124</v>
+        <v>130141177</v>
       </c>
       <c r="B85" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9659,10 +9650,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>408276</v>
+        <v>408429</v>
       </c>
       <c r="R85" t="n">
-        <v>6771996</v>
+        <v>6771723</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9694,7 +9685,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9704,7 +9695,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9731,10 +9722,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>130141131</v>
+        <v>130141170</v>
       </c>
       <c r="B86" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9766,10 +9757,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>408169</v>
+        <v>408080</v>
       </c>
       <c r="R86" t="n">
-        <v>6771937</v>
+        <v>6772000</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9801,7 +9792,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9811,7 +9802,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9838,10 +9829,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>130141173</v>
+        <v>130141110</v>
       </c>
       <c r="B87" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9873,10 +9864,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>408388</v>
+        <v>408466</v>
       </c>
       <c r="R87" t="n">
-        <v>6771760</v>
+        <v>6771924</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9908,7 +9899,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9918,7 +9909,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9945,10 +9936,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>130141177</v>
+        <v>130141124</v>
       </c>
       <c r="B88" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9980,10 +9971,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>408429</v>
+        <v>408276</v>
       </c>
       <c r="R88" t="n">
-        <v>6771723</v>
+        <v>6771996</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10015,7 +10006,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10025,7 +10016,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10052,10 +10043,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>130141170</v>
+        <v>130141131</v>
       </c>
       <c r="B89" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10087,10 +10078,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>408080</v>
+        <v>408169</v>
       </c>
       <c r="R89" t="n">
-        <v>6772000</v>
+        <v>6771937</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10122,7 +10113,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10132,7 +10123,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10159,45 +10150,54 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>130141110</v>
+        <v>130141094</v>
       </c>
       <c r="B90" t="n">
-        <v>79183</v>
+        <v>98949</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>408466</v>
+        <v>408187</v>
       </c>
       <c r="R90" t="n">
-        <v>6771924</v>
+        <v>6771901</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10229,7 +10229,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10239,7 +10239,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD90" t="b">

--- a/artfynd/A 60367-2025 artfynd.xlsx
+++ b/artfynd/A 60367-2025 artfynd.xlsx
@@ -2815,32 +2815,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130141130</v>
+        <v>130141041</v>
       </c>
       <c r="B22" t="n">
-        <v>79209</v>
+        <v>91721</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>408179</v>
+        <v>408520</v>
       </c>
       <c r="R22" t="n">
-        <v>6771918</v>
+        <v>6772210</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2922,45 +2922,50 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130141041</v>
+        <v>130141053</v>
       </c>
       <c r="B23" t="n">
-        <v>91721</v>
+        <v>57849</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>408520</v>
+        <v>408180</v>
       </c>
       <c r="R23" t="n">
-        <v>6772210</v>
+        <v>6771921</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2992,7 +2997,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3002,7 +3007,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3029,10 +3034,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130141053</v>
+        <v>130141130</v>
       </c>
       <c r="B24" t="n">
-        <v>57849</v>
+        <v>79209</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3040,39 +3045,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>408180</v>
+        <v>408179</v>
       </c>
       <c r="R24" t="n">
-        <v>6771921</v>
+        <v>6771918</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3141,45 +3141,54 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130141043</v>
+        <v>130141100</v>
       </c>
       <c r="B25" t="n">
-        <v>91757</v>
+        <v>98949</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>408279</v>
+        <v>408055</v>
       </c>
       <c r="R25" t="n">
-        <v>6771971</v>
+        <v>6772067</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3211,7 +3220,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3221,7 +3230,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3248,10 +3257,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130141114</v>
+        <v>130141049</v>
       </c>
       <c r="B26" t="n">
-        <v>79209</v>
+        <v>91708</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3259,21 +3268,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3283,10 +3292,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>408422</v>
+        <v>408266</v>
       </c>
       <c r="R26" t="n">
-        <v>6771930</v>
+        <v>6771955</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3318,7 +3327,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3328,7 +3337,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3355,54 +3364,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130141100</v>
+        <v>130141043</v>
       </c>
       <c r="B27" t="n">
-        <v>98949</v>
+        <v>91757</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>408055</v>
+        <v>408279</v>
       </c>
       <c r="R27" t="n">
-        <v>6772067</v>
+        <v>6771971</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3471,10 +3471,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130141049</v>
+        <v>130141114</v>
       </c>
       <c r="B28" t="n">
-        <v>91708</v>
+        <v>79209</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3482,21 +3482,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3506,10 +3506,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>408266</v>
+        <v>408422</v>
       </c>
       <c r="R28" t="n">
-        <v>6771955</v>
+        <v>6771930</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -5421,32 +5421,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130141103</v>
+        <v>130141105</v>
       </c>
       <c r="B46" t="n">
-        <v>80280</v>
+        <v>91771</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>229748</v>
+        <v>1204</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5456,10 +5456,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>408441</v>
+        <v>408032</v>
       </c>
       <c r="R46" t="n">
-        <v>6771723</v>
+        <v>6772075</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5491,7 +5491,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5510,7 +5510,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5529,32 +5528,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130141105</v>
+        <v>130141073</v>
       </c>
       <c r="B47" t="n">
-        <v>91771</v>
+        <v>80342</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1204</v>
+        <v>6461</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5564,10 +5563,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>408032</v>
+        <v>408029</v>
       </c>
       <c r="R47" t="n">
-        <v>6772075</v>
+        <v>6771956</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5599,7 +5598,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5609,7 +5608,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5636,32 +5635,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130141073</v>
+        <v>130141128</v>
       </c>
       <c r="B48" t="n">
-        <v>80342</v>
+        <v>79209</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5671,10 +5670,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>408029</v>
+        <v>408213</v>
       </c>
       <c r="R48" t="n">
-        <v>6771956</v>
+        <v>6771880</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5706,7 +5705,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5716,7 +5715,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5743,7 +5742,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130141128</v>
+        <v>130141184</v>
       </c>
       <c r="B49" t="n">
         <v>79209</v>
@@ -5778,10 +5777,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>408213</v>
+        <v>408448</v>
       </c>
       <c r="R49" t="n">
-        <v>6771880</v>
+        <v>6771990</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5813,7 +5812,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5823,7 +5822,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5850,7 +5849,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130141184</v>
+        <v>130141123</v>
       </c>
       <c r="B50" t="n">
         <v>79209</v>
@@ -5885,10 +5884,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>408448</v>
+        <v>408291</v>
       </c>
       <c r="R50" t="n">
-        <v>6771990</v>
+        <v>6771913</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5920,7 +5919,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5930,7 +5929,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5957,7 +5956,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130141123</v>
+        <v>130141120</v>
       </c>
       <c r="B51" t="n">
         <v>79209</v>
@@ -5992,10 +5991,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>408291</v>
+        <v>408363</v>
       </c>
       <c r="R51" t="n">
-        <v>6771913</v>
+        <v>6771889</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6027,7 +6026,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6037,7 +6036,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6064,32 +6063,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130141120</v>
+        <v>130141103</v>
       </c>
       <c r="B52" t="n">
-        <v>79209</v>
+        <v>80280</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>229748</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6099,10 +6098,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>408363</v>
+        <v>408441</v>
       </c>
       <c r="R52" t="n">
-        <v>6771889</v>
+        <v>6771723</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6134,7 +6133,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6144,7 +6143,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6153,6 +6152,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -7023,32 +7023,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130141040</v>
+        <v>130141195</v>
       </c>
       <c r="B61" t="n">
-        <v>91721</v>
+        <v>89151</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5447</v>
+        <v>510</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7058,10 +7058,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>408073</v>
+        <v>408282</v>
       </c>
       <c r="R61" t="n">
-        <v>6772016</v>
+        <v>6771935</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7093,7 +7093,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7103,7 +7103,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7130,7 +7130,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130141035</v>
+        <v>130141040</v>
       </c>
       <c r="B62" t="n">
         <v>91721</v>
@@ -7165,10 +7165,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>408053</v>
+        <v>408073</v>
       </c>
       <c r="R62" t="n">
-        <v>6772152</v>
+        <v>6772016</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7210,7 +7210,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7237,32 +7237,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130141174</v>
+        <v>130141035</v>
       </c>
       <c r="B63" t="n">
-        <v>79209</v>
+        <v>91721</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7272,10 +7272,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>408396</v>
+        <v>408053</v>
       </c>
       <c r="R63" t="n">
-        <v>6771759</v>
+        <v>6772152</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7307,7 +7307,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7344,10 +7344,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130141195</v>
+        <v>130141174</v>
       </c>
       <c r="B64" t="n">
-        <v>89151</v>
+        <v>79209</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7355,21 +7355,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7379,10 +7379,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>408282</v>
+        <v>408396</v>
       </c>
       <c r="R64" t="n">
-        <v>6771935</v>
+        <v>6771759</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7414,7 +7414,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7424,7 +7424,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7451,32 +7451,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130141168</v>
+        <v>130141071</v>
       </c>
       <c r="B65" t="n">
-        <v>79209</v>
+        <v>97820</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7486,10 +7486,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>408044</v>
+        <v>408448</v>
       </c>
       <c r="R65" t="n">
-        <v>6772152</v>
+        <v>6771891</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7521,7 +7521,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7558,32 +7558,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130141071</v>
+        <v>130141168</v>
       </c>
       <c r="B66" t="n">
-        <v>97820</v>
+        <v>79209</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7593,10 +7593,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>408448</v>
+        <v>408044</v>
       </c>
       <c r="R66" t="n">
-        <v>6771891</v>
+        <v>6772152</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7628,7 +7628,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7638,7 +7638,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8102,10 +8102,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130141055</v>
+        <v>130141048</v>
       </c>
       <c r="B71" t="n">
-        <v>57849</v>
+        <v>91757</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8113,39 +8113,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>408062</v>
+        <v>408067</v>
       </c>
       <c r="R71" t="n">
-        <v>6771974</v>
+        <v>6772051</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8177,7 +8172,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8187,7 +8182,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8214,32 +8209,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130141048</v>
+        <v>130141037</v>
       </c>
       <c r="B72" t="n">
-        <v>91757</v>
+        <v>91721</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8249,10 +8244,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>408067</v>
+        <v>408048</v>
       </c>
       <c r="R72" t="n">
-        <v>6772051</v>
+        <v>6772154</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8284,7 +8279,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8294,7 +8289,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8321,45 +8316,50 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130141037</v>
+        <v>130141055</v>
       </c>
       <c r="B73" t="n">
-        <v>91721</v>
+        <v>57849</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>408048</v>
+        <v>408062</v>
       </c>
       <c r="R73" t="n">
-        <v>6772154</v>
+        <v>6771974</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8391,7 +8391,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8401,7 +8401,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD73" t="b">

--- a/artfynd/A 60367-2025 artfynd.xlsx
+++ b/artfynd/A 60367-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130141062</v>
       </c>
       <c r="B2" t="n">
-        <v>97820</v>
+        <v>97821</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130141111</v>
+        <v>130141171</v>
       </c>
       <c r="B3" t="n">
         <v>79209</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>408452</v>
+        <v>408023</v>
       </c>
       <c r="R3" t="n">
-        <v>6771936</v>
+        <v>6771952</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130141118</v>
+        <v>130141191</v>
       </c>
       <c r="B4" t="n">
         <v>79209</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>408392</v>
+        <v>408509</v>
       </c>
       <c r="R4" t="n">
-        <v>6771906</v>
+        <v>6772194</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130141171</v>
+        <v>130141190</v>
       </c>
       <c r="B5" t="n">
         <v>79209</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>408023</v>
+        <v>408513</v>
       </c>
       <c r="R5" t="n">
-        <v>6771952</v>
+        <v>6772199</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130141179</v>
+        <v>130141111</v>
       </c>
       <c r="B6" t="n">
         <v>79209</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>408446</v>
+        <v>408452</v>
       </c>
       <c r="R6" t="n">
-        <v>6771725</v>
+        <v>6771936</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130141190</v>
+        <v>130141118</v>
       </c>
       <c r="B7" t="n">
         <v>79209</v>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>408513</v>
+        <v>408392</v>
       </c>
       <c r="R7" t="n">
-        <v>6772199</v>
+        <v>6771906</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130141191</v>
+        <v>130141179</v>
       </c>
       <c r="B8" t="n">
         <v>79209</v>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>408509</v>
+        <v>408446</v>
       </c>
       <c r="R8" t="n">
-        <v>6772194</v>
+        <v>6771725</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1427,7 +1427,7 @@
         <v>130141045</v>
       </c>
       <c r="B9" t="n">
-        <v>91757</v>
+        <v>91758</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130141134</v>
+        <v>130141185</v>
       </c>
       <c r="B10" t="n">
         <v>79209</v>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>408063</v>
+        <v>408470</v>
       </c>
       <c r="R10" t="n">
-        <v>6771997</v>
+        <v>6772171</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,7 +1638,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130141185</v>
+        <v>130141109</v>
       </c>
       <c r="B11" t="n">
         <v>79209</v>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>408470</v>
+        <v>408039</v>
       </c>
       <c r="R11" t="n">
-        <v>6772171</v>
+        <v>6771959</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,7 +1745,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130141109</v>
+        <v>130141176</v>
       </c>
       <c r="B12" t="n">
         <v>79209</v>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>408039</v>
+        <v>408421</v>
       </c>
       <c r="R12" t="n">
-        <v>6771959</v>
+        <v>6771727</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,7 +1852,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130141176</v>
+        <v>130141134</v>
       </c>
       <c r="B13" t="n">
         <v>79209</v>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>408421</v>
+        <v>408063</v>
       </c>
       <c r="R13" t="n">
-        <v>6771727</v>
+        <v>6771997</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,7 +1959,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130141182</v>
+        <v>130141169</v>
       </c>
       <c r="B14" t="n">
         <v>79209</v>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>408444</v>
+        <v>408069</v>
       </c>
       <c r="R14" t="n">
-        <v>6771919</v>
+        <v>6772125</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,7 +2066,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130141169</v>
+        <v>130141133</v>
       </c>
       <c r="B15" t="n">
         <v>79209</v>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>408069</v>
+        <v>408053</v>
       </c>
       <c r="R15" t="n">
-        <v>6772125</v>
+        <v>6771991</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,7 +2173,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130141125</v>
+        <v>130141180</v>
       </c>
       <c r="B16" t="n">
         <v>79209</v>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>408263</v>
+        <v>408470</v>
       </c>
       <c r="R16" t="n">
-        <v>6771960</v>
+        <v>6771816</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,7 +2280,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130141133</v>
+        <v>130141125</v>
       </c>
       <c r="B17" t="n">
         <v>79209</v>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>408053</v>
+        <v>408263</v>
       </c>
       <c r="R17" t="n">
-        <v>6771991</v>
+        <v>6771960</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2387,7 +2387,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130141180</v>
+        <v>130141182</v>
       </c>
       <c r="B18" t="n">
         <v>79209</v>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>408470</v>
+        <v>408444</v>
       </c>
       <c r="R18" t="n">
-        <v>6771816</v>
+        <v>6771919</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2497,7 +2497,7 @@
         <v>130141068</v>
       </c>
       <c r="B19" t="n">
-        <v>97820</v>
+        <v>97821</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2601,32 +2601,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130141201</v>
+        <v>130141059</v>
       </c>
       <c r="B20" t="n">
-        <v>92414</v>
+        <v>92211</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1965</v>
+        <v>1209</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Citronporing</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Antrodiella citrinella</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Ryvarden</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2636,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>408238</v>
+        <v>408213</v>
       </c>
       <c r="R20" t="n">
-        <v>6771897</v>
+        <v>6771880</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2708,32 +2708,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130141059</v>
+        <v>130141041</v>
       </c>
       <c r="B21" t="n">
-        <v>92210</v>
+        <v>91722</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2743,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>408213</v>
+        <v>408520</v>
       </c>
       <c r="R21" t="n">
-        <v>6771880</v>
+        <v>6772210</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2815,32 +2815,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130141041</v>
+        <v>130141201</v>
       </c>
       <c r="B22" t="n">
-        <v>91721</v>
+        <v>92415</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>1965</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Citronporing</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Antrodiella citrinella</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Niemelä &amp; Ryvarden</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>408520</v>
+        <v>408238</v>
       </c>
       <c r="R22" t="n">
-        <v>6772210</v>
+        <v>6771897</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2922,10 +2922,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130141053</v>
+        <v>130141130</v>
       </c>
       <c r="B23" t="n">
-        <v>57849</v>
+        <v>79209</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2933,39 +2933,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>408180</v>
+        <v>408179</v>
       </c>
       <c r="R23" t="n">
-        <v>6771921</v>
+        <v>6771918</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3034,10 +3029,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130141130</v>
+        <v>130141053</v>
       </c>
       <c r="B24" t="n">
-        <v>79209</v>
+        <v>57849</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3045,34 +3040,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>408179</v>
+        <v>408180</v>
       </c>
       <c r="R24" t="n">
-        <v>6771918</v>
+        <v>6771921</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3144,7 +3144,7 @@
         <v>130141100</v>
       </c>
       <c r="B25" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3257,10 +3257,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130141049</v>
+        <v>130141043</v>
       </c>
       <c r="B26" t="n">
-        <v>91708</v>
+        <v>91758</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3268,21 +3268,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>112</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3292,10 +3292,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>408266</v>
+        <v>408279</v>
       </c>
       <c r="R26" t="n">
-        <v>6771955</v>
+        <v>6771971</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3327,7 +3327,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3364,10 +3364,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130141043</v>
+        <v>130141188</v>
       </c>
       <c r="B27" t="n">
-        <v>91757</v>
+        <v>79209</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3375,21 +3375,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3399,10 +3399,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>408279</v>
+        <v>408452</v>
       </c>
       <c r="R27" t="n">
-        <v>6771971</v>
+        <v>6772262</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3578,10 +3578,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130141188</v>
+        <v>130141049</v>
       </c>
       <c r="B29" t="n">
-        <v>79209</v>
+        <v>91709</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3589,21 +3589,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>408452</v>
+        <v>408266</v>
       </c>
       <c r="R29" t="n">
-        <v>6772262</v>
+        <v>6771955</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3688,7 +3688,7 @@
         <v>130141042</v>
       </c>
       <c r="B30" t="n">
-        <v>91757</v>
+        <v>91758</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130141122</v>
+        <v>130141126</v>
       </c>
       <c r="B31" t="n">
         <v>79209</v>
@@ -3827,10 +3827,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>408301</v>
+        <v>408233</v>
       </c>
       <c r="R31" t="n">
-        <v>6771872</v>
+        <v>6771939</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3899,7 +3899,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130141178</v>
+        <v>130141122</v>
       </c>
       <c r="B32" t="n">
         <v>79209</v>
@@ -3934,10 +3934,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>408446</v>
+        <v>408301</v>
       </c>
       <c r="R32" t="n">
-        <v>6771720</v>
+        <v>6771872</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3969,7 +3969,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4006,7 +4006,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130141192</v>
+        <v>130141187</v>
       </c>
       <c r="B33" t="n">
         <v>79209</v>
@@ -4041,10 +4041,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>408522</v>
+        <v>408448</v>
       </c>
       <c r="R33" t="n">
-        <v>6772172</v>
+        <v>6772196</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4113,7 +4113,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130141126</v>
+        <v>130141192</v>
       </c>
       <c r="B34" t="n">
         <v>79209</v>
@@ -4148,10 +4148,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>408233</v>
+        <v>408522</v>
       </c>
       <c r="R34" t="n">
-        <v>6771939</v>
+        <v>6772172</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4183,7 +4183,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4220,7 +4220,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130141187</v>
+        <v>130141178</v>
       </c>
       <c r="B35" t="n">
         <v>79209</v>
@@ -4255,10 +4255,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>408448</v>
+        <v>408446</v>
       </c>
       <c r="R35" t="n">
-        <v>6772196</v>
+        <v>6771720</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4290,7 +4290,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4300,7 +4300,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4327,54 +4327,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130141096</v>
+        <v>130141038</v>
       </c>
       <c r="B36" t="n">
-        <v>98949</v>
+        <v>91722</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>408022</v>
+        <v>408067</v>
       </c>
       <c r="R36" t="n">
-        <v>6772065</v>
+        <v>6772053</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4406,7 +4397,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4416,7 +4407,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4443,45 +4434,54 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130141038</v>
+        <v>130141096</v>
       </c>
       <c r="B37" t="n">
-        <v>91721</v>
+        <v>98950</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>408067</v>
+        <v>408022</v>
       </c>
       <c r="R37" t="n">
-        <v>6772053</v>
+        <v>6772065</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4513,7 +4513,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4523,7 +4523,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4550,7 +4550,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130141175</v>
+        <v>130141136</v>
       </c>
       <c r="B38" t="n">
         <v>79209</v>
@@ -4585,10 +4585,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>408404</v>
+        <v>408031</v>
       </c>
       <c r="R38" t="n">
-        <v>6771749</v>
+        <v>6772025</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4620,7 +4620,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4630,7 +4630,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4657,7 +4657,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130141136</v>
+        <v>130141175</v>
       </c>
       <c r="B39" t="n">
         <v>79209</v>
@@ -4692,10 +4692,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>408031</v>
+        <v>408404</v>
       </c>
       <c r="R39" t="n">
-        <v>6772025</v>
+        <v>6771749</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4727,7 +4727,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4767,7 +4767,7 @@
         <v>130141108</v>
       </c>
       <c r="B40" t="n">
-        <v>91777</v>
+        <v>91778</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5089,7 +5089,7 @@
         <v>130141101</v>
       </c>
       <c r="B43" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5202,45 +5202,50 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130141060</v>
+        <v>130141029</v>
       </c>
       <c r="B44" t="n">
-        <v>92210</v>
+        <v>5197</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1209</v>
+        <v>105930</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>408215</v>
+        <v>408243</v>
       </c>
       <c r="R44" t="n">
-        <v>6771888</v>
+        <v>6771879</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5272,7 +5277,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5282,7 +5287,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5309,50 +5314,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130141029</v>
+        <v>130141060</v>
       </c>
       <c r="B45" t="n">
-        <v>5197</v>
+        <v>92211</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>105930</v>
+        <v>1209</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>408243</v>
+        <v>408215</v>
       </c>
       <c r="R45" t="n">
-        <v>6771879</v>
+        <v>6771888</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5384,7 +5384,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5394,7 +5394,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5424,7 +5424,7 @@
         <v>130141105</v>
       </c>
       <c r="B46" t="n">
-        <v>91771</v>
+        <v>91772</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5635,7 +5635,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130141128</v>
+        <v>130141184</v>
       </c>
       <c r="B48" t="n">
         <v>79209</v>
@@ -5670,10 +5670,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>408213</v>
+        <v>408448</v>
       </c>
       <c r="R48" t="n">
-        <v>6771880</v>
+        <v>6771990</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5705,7 +5705,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5715,7 +5715,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5742,7 +5742,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130141184</v>
+        <v>130141123</v>
       </c>
       <c r="B49" t="n">
         <v>79209</v>
@@ -5777,10 +5777,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>408448</v>
+        <v>408291</v>
       </c>
       <c r="R49" t="n">
-        <v>6771990</v>
+        <v>6771913</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5812,7 +5812,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5822,7 +5822,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5849,7 +5849,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130141123</v>
+        <v>130141128</v>
       </c>
       <c r="B50" t="n">
         <v>79209</v>
@@ -5884,10 +5884,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>408291</v>
+        <v>408213</v>
       </c>
       <c r="R50" t="n">
-        <v>6771913</v>
+        <v>6771880</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5919,7 +5919,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5929,7 +5929,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6171,10 +6171,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130141196</v>
+        <v>130141107</v>
       </c>
       <c r="B53" t="n">
-        <v>89151</v>
+        <v>91778</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6182,23 +6182,19 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6206,10 +6202,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>408233</v>
+        <v>408453</v>
       </c>
       <c r="R53" t="n">
-        <v>6771921</v>
+        <v>6771936</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6241,7 +6237,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6251,7 +6247,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6278,32 +6274,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130141137</v>
+        <v>130141064</v>
       </c>
       <c r="B54" t="n">
-        <v>79209</v>
+        <v>97821</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6313,10 +6309,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>408034</v>
+        <v>408256</v>
       </c>
       <c r="R54" t="n">
-        <v>6772034</v>
+        <v>6771965</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6348,7 +6344,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6358,7 +6354,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6385,10 +6381,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130141107</v>
+        <v>130141196</v>
       </c>
       <c r="B55" t="n">
-        <v>91777</v>
+        <v>89152</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6396,19 +6392,23 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr"/>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6416,10 +6416,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>408453</v>
+        <v>408233</v>
       </c>
       <c r="R55" t="n">
-        <v>6771936</v>
+        <v>6771921</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6451,7 +6451,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6488,7 +6488,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130141189</v>
+        <v>130141115</v>
       </c>
       <c r="B56" t="n">
         <v>79209</v>
@@ -6523,10 +6523,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>408512</v>
+        <v>408423</v>
       </c>
       <c r="R56" t="n">
-        <v>6772218</v>
+        <v>6771906</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6558,7 +6558,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6568,7 +6568,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6595,7 +6595,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130141135</v>
+        <v>130141189</v>
       </c>
       <c r="B57" t="n">
         <v>79209</v>
@@ -6630,10 +6630,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>408031</v>
+        <v>408512</v>
       </c>
       <c r="R57" t="n">
-        <v>6772014</v>
+        <v>6772218</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6665,7 +6665,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6675,7 +6675,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6702,7 +6702,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130141115</v>
+        <v>130141137</v>
       </c>
       <c r="B58" t="n">
         <v>79209</v>
@@ -6737,10 +6737,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>408423</v>
+        <v>408034</v>
       </c>
       <c r="R58" t="n">
-        <v>6771906</v>
+        <v>6772034</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6772,7 +6772,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6782,7 +6782,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6809,7 +6809,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130141117</v>
+        <v>130141135</v>
       </c>
       <c r="B59" t="n">
         <v>79209</v>
@@ -6844,10 +6844,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>408409</v>
+        <v>408031</v>
       </c>
       <c r="R59" t="n">
-        <v>6771881</v>
+        <v>6772014</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6916,32 +6916,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130141064</v>
+        <v>130141117</v>
       </c>
       <c r="B60" t="n">
-        <v>97820</v>
+        <v>79209</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6951,10 +6951,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>408256</v>
+        <v>408409</v>
       </c>
       <c r="R60" t="n">
-        <v>6771965</v>
+        <v>6771881</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6986,7 +6986,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6996,7 +6996,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7026,7 +7026,7 @@
         <v>130141195</v>
       </c>
       <c r="B61" t="n">
-        <v>89151</v>
+        <v>89152</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7130,32 +7130,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130141040</v>
+        <v>130141174</v>
       </c>
       <c r="B62" t="n">
-        <v>91721</v>
+        <v>79209</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7165,10 +7165,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>408073</v>
+        <v>408396</v>
       </c>
       <c r="R62" t="n">
-        <v>6772016</v>
+        <v>6771759</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7210,7 +7210,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7237,10 +7237,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130141035</v>
+        <v>130141040</v>
       </c>
       <c r="B63" t="n">
-        <v>91721</v>
+        <v>91722</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7272,10 +7272,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>408053</v>
+        <v>408073</v>
       </c>
       <c r="R63" t="n">
-        <v>6772152</v>
+        <v>6772016</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7307,7 +7307,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7344,32 +7344,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130141174</v>
+        <v>130141035</v>
       </c>
       <c r="B64" t="n">
-        <v>79209</v>
+        <v>91722</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7379,10 +7379,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>408396</v>
+        <v>408053</v>
       </c>
       <c r="R64" t="n">
-        <v>6771759</v>
+        <v>6772152</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7414,7 +7414,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7424,7 +7424,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7454,7 +7454,7 @@
         <v>130141071</v>
       </c>
       <c r="B65" t="n">
-        <v>97820</v>
+        <v>97821</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7668,7 +7668,7 @@
         <v>130141098</v>
       </c>
       <c r="B67" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7781,7 +7781,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130141138</v>
+        <v>130141119</v>
       </c>
       <c r="B68" t="n">
         <v>79209</v>
@@ -7816,10 +7816,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>408043</v>
+        <v>408380</v>
       </c>
       <c r="R68" t="n">
-        <v>6772111</v>
+        <v>6771903</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7851,7 +7851,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7861,7 +7861,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7888,7 +7888,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130141112</v>
+        <v>130141138</v>
       </c>
       <c r="B69" t="n">
         <v>79209</v>
@@ -7923,10 +7923,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>408432</v>
+        <v>408043</v>
       </c>
       <c r="R69" t="n">
-        <v>6771948</v>
+        <v>6772111</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7958,7 +7958,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7968,7 +7968,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7995,7 +7995,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130141119</v>
+        <v>130141112</v>
       </c>
       <c r="B70" t="n">
         <v>79209</v>
@@ -8030,10 +8030,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>408380</v>
+        <v>408432</v>
       </c>
       <c r="R70" t="n">
-        <v>6771903</v>
+        <v>6771948</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8065,7 +8065,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8105,7 +8105,7 @@
         <v>130141048</v>
       </c>
       <c r="B71" t="n">
-        <v>91757</v>
+        <v>91758</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8212,7 +8212,7 @@
         <v>130141037</v>
       </c>
       <c r="B72" t="n">
-        <v>91721</v>
+        <v>91722</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8431,7 +8431,7 @@
         <v>130141070</v>
       </c>
       <c r="B74" t="n">
-        <v>97820</v>
+        <v>97821</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8535,10 +8535,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130141183</v>
+        <v>130141194</v>
       </c>
       <c r="B75" t="n">
-        <v>79209</v>
+        <v>89152</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8546,21 +8546,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8570,13 +8570,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>408441</v>
+        <v>408303</v>
       </c>
       <c r="R75" t="n">
-        <v>6771967</v>
+        <v>6771876</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8615,7 +8615,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8642,7 +8642,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130141181</v>
+        <v>130141116</v>
       </c>
       <c r="B76" t="n">
         <v>79209</v>
@@ -8677,10 +8677,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>408466</v>
+        <v>408411</v>
       </c>
       <c r="R76" t="n">
-        <v>6771845</v>
+        <v>6771863</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8722,7 +8722,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8749,7 +8749,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>130141116</v>
+        <v>130141181</v>
       </c>
       <c r="B77" t="n">
         <v>79209</v>
@@ -8784,10 +8784,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>408411</v>
+        <v>408466</v>
       </c>
       <c r="R77" t="n">
-        <v>6771863</v>
+        <v>6771845</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8819,7 +8819,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8829,7 +8829,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8856,10 +8856,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>130141194</v>
+        <v>130141183</v>
       </c>
       <c r="B78" t="n">
-        <v>89151</v>
+        <v>79209</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8867,21 +8867,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8891,13 +8891,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>408303</v>
+        <v>408441</v>
       </c>
       <c r="R78" t="n">
-        <v>6771876</v>
+        <v>6771967</v>
       </c>
       <c r="S78" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8926,7 +8926,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8936,7 +8936,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9187,10 +9187,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>130141069</v>
+        <v>130141063</v>
       </c>
       <c r="B81" t="n">
-        <v>97820</v>
+        <v>97821</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9222,10 +9222,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>408016</v>
+        <v>408291</v>
       </c>
       <c r="R81" t="n">
-        <v>6771944</v>
+        <v>6771923</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9257,7 +9257,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9294,10 +9294,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>130141063</v>
+        <v>130141069</v>
       </c>
       <c r="B82" t="n">
-        <v>97820</v>
+        <v>97821</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9329,10 +9329,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>408291</v>
+        <v>408016</v>
       </c>
       <c r="R82" t="n">
-        <v>6771923</v>
+        <v>6771944</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9364,7 +9364,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9374,7 +9374,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9508,45 +9508,54 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>130141173</v>
+        <v>130141094</v>
       </c>
       <c r="B84" t="n">
-        <v>79209</v>
+        <v>98950</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>408388</v>
+        <v>408187</v>
       </c>
       <c r="R84" t="n">
-        <v>6771760</v>
+        <v>6771901</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9578,7 +9587,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9588,7 +9597,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9615,7 +9624,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>130141177</v>
+        <v>130141173</v>
       </c>
       <c r="B85" t="n">
         <v>79209</v>
@@ -9650,10 +9659,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>408429</v>
+        <v>408388</v>
       </c>
       <c r="R85" t="n">
-        <v>6771723</v>
+        <v>6771760</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9685,7 +9694,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9695,7 +9704,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9829,7 +9838,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>130141110</v>
+        <v>130141177</v>
       </c>
       <c r="B87" t="n">
         <v>79209</v>
@@ -9864,10 +9873,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>408466</v>
+        <v>408429</v>
       </c>
       <c r="R87" t="n">
-        <v>6771924</v>
+        <v>6771723</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9899,7 +9908,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9909,7 +9918,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9936,7 +9945,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>130141124</v>
+        <v>130141110</v>
       </c>
       <c r="B88" t="n">
         <v>79209</v>
@@ -9971,10 +9980,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>408276</v>
+        <v>408466</v>
       </c>
       <c r="R88" t="n">
-        <v>6771996</v>
+        <v>6771924</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10006,7 +10015,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10016,7 +10025,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10150,54 +10159,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>130141094</v>
+        <v>130141124</v>
       </c>
       <c r="B90" t="n">
-        <v>98949</v>
+        <v>79209</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>408187</v>
+        <v>408276</v>
       </c>
       <c r="R90" t="n">
-        <v>6771901</v>
+        <v>6771996</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10229,7 +10229,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10239,7 +10239,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD90" t="b">

--- a/artfynd/A 60367-2025 artfynd.xlsx
+++ b/artfynd/A 60367-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130141062</v>
+        <v>130141111</v>
       </c>
       <c r="B2" t="n">
-        <v>97821</v>
+        <v>79209</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>408421</v>
+        <v>408452</v>
       </c>
       <c r="R2" t="n">
-        <v>6771953</v>
+        <v>6771936</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130141171</v>
+        <v>130141118</v>
       </c>
       <c r="B3" t="n">
         <v>79209</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>408023</v>
+        <v>408392</v>
       </c>
       <c r="R3" t="n">
-        <v>6771952</v>
+        <v>6771906</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130141191</v>
+        <v>130141171</v>
       </c>
       <c r="B4" t="n">
         <v>79209</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>408509</v>
+        <v>408023</v>
       </c>
       <c r="R4" t="n">
-        <v>6772194</v>
+        <v>6771952</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130141190</v>
+        <v>130141179</v>
       </c>
       <c r="B5" t="n">
         <v>79209</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>408513</v>
+        <v>408446</v>
       </c>
       <c r="R5" t="n">
-        <v>6772199</v>
+        <v>6771725</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130141111</v>
+        <v>130141190</v>
       </c>
       <c r="B6" t="n">
         <v>79209</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>408452</v>
+        <v>408513</v>
       </c>
       <c r="R6" t="n">
-        <v>6771936</v>
+        <v>6772199</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130141118</v>
+        <v>130141191</v>
       </c>
       <c r="B7" t="n">
         <v>79209</v>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>408392</v>
+        <v>408509</v>
       </c>
       <c r="R7" t="n">
-        <v>6771906</v>
+        <v>6772194</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,32 +1317,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130141179</v>
+        <v>130141062</v>
       </c>
       <c r="B8" t="n">
-        <v>79209</v>
+        <v>97822</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>408446</v>
+        <v>408421</v>
       </c>
       <c r="R8" t="n">
-        <v>6771725</v>
+        <v>6771953</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1427,7 +1427,7 @@
         <v>130141045</v>
       </c>
       <c r="B9" t="n">
-        <v>91758</v>
+        <v>91759</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130141185</v>
+        <v>130141134</v>
       </c>
       <c r="B10" t="n">
         <v>79209</v>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>408470</v>
+        <v>408063</v>
       </c>
       <c r="R10" t="n">
-        <v>6772171</v>
+        <v>6771997</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,7 +1638,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130141109</v>
+        <v>130141185</v>
       </c>
       <c r="B11" t="n">
         <v>79209</v>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>408039</v>
+        <v>408470</v>
       </c>
       <c r="R11" t="n">
-        <v>6771959</v>
+        <v>6772171</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,7 +1745,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130141176</v>
+        <v>130141109</v>
       </c>
       <c r="B12" t="n">
         <v>79209</v>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>408421</v>
+        <v>408039</v>
       </c>
       <c r="R12" t="n">
-        <v>6771727</v>
+        <v>6771959</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,7 +1852,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130141134</v>
+        <v>130141176</v>
       </c>
       <c r="B13" t="n">
         <v>79209</v>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>408063</v>
+        <v>408421</v>
       </c>
       <c r="R13" t="n">
-        <v>6771997</v>
+        <v>6771727</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,32 +1959,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130141169</v>
+        <v>130141068</v>
       </c>
       <c r="B14" t="n">
-        <v>79209</v>
+        <v>97822</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>408069</v>
+        <v>408061</v>
       </c>
       <c r="R14" t="n">
-        <v>6772125</v>
+        <v>6772069</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,7 +2066,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130141133</v>
+        <v>130141182</v>
       </c>
       <c r="B15" t="n">
         <v>79209</v>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>408053</v>
+        <v>408444</v>
       </c>
       <c r="R15" t="n">
-        <v>6771991</v>
+        <v>6771919</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,7 +2173,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130141180</v>
+        <v>130141169</v>
       </c>
       <c r="B16" t="n">
         <v>79209</v>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>408470</v>
+        <v>408069</v>
       </c>
       <c r="R16" t="n">
-        <v>6771816</v>
+        <v>6772125</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2387,7 +2387,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130141182</v>
+        <v>130141133</v>
       </c>
       <c r="B18" t="n">
         <v>79209</v>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>408444</v>
+        <v>408053</v>
       </c>
       <c r="R18" t="n">
-        <v>6771919</v>
+        <v>6771991</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2494,32 +2494,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130141068</v>
+        <v>130141180</v>
       </c>
       <c r="B19" t="n">
-        <v>97821</v>
+        <v>79209</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>408061</v>
+        <v>408470</v>
       </c>
       <c r="R19" t="n">
-        <v>6772069</v>
+        <v>6771816</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2604,7 +2604,7 @@
         <v>130141059</v>
       </c>
       <c r="B20" t="n">
-        <v>92211</v>
+        <v>92212</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2708,32 +2708,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130141041</v>
+        <v>130141201</v>
       </c>
       <c r="B21" t="n">
-        <v>91722</v>
+        <v>92416</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>1965</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Citronporing</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Antrodiella citrinella</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Niemelä &amp; Ryvarden</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2743,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>408520</v>
+        <v>408238</v>
       </c>
       <c r="R21" t="n">
-        <v>6772210</v>
+        <v>6771897</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2815,32 +2815,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130141201</v>
+        <v>130141041</v>
       </c>
       <c r="B22" t="n">
-        <v>92415</v>
+        <v>91723</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1965</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Citronporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Antrodiella citrinella</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Ryvarden</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>408238</v>
+        <v>408520</v>
       </c>
       <c r="R22" t="n">
-        <v>6771897</v>
+        <v>6772210</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3144,7 +3144,7 @@
         <v>130141100</v>
       </c>
       <c r="B25" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         <v>130141043</v>
       </c>
       <c r="B26" t="n">
-        <v>91758</v>
+        <v>91759</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>130141049</v>
       </c>
       <c r="B29" t="n">
-        <v>91709</v>
+        <v>91710</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3685,10 +3685,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130141042</v>
+        <v>130141178</v>
       </c>
       <c r="B30" t="n">
-        <v>91758</v>
+        <v>79209</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3696,21 +3696,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3720,10 +3720,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>408420</v>
+        <v>408446</v>
       </c>
       <c r="R30" t="n">
-        <v>6771911</v>
+        <v>6771720</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3765,7 +3765,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3792,7 +3792,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130141126</v>
+        <v>130141192</v>
       </c>
       <c r="B31" t="n">
         <v>79209</v>
@@ -3827,10 +3827,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>408233</v>
+        <v>408522</v>
       </c>
       <c r="R31" t="n">
-        <v>6771939</v>
+        <v>6772172</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4006,7 +4006,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130141187</v>
+        <v>130141126</v>
       </c>
       <c r="B33" t="n">
         <v>79209</v>
@@ -4041,10 +4041,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>408448</v>
+        <v>408233</v>
       </c>
       <c r="R33" t="n">
-        <v>6772196</v>
+        <v>6771939</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4113,7 +4113,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130141192</v>
+        <v>130141187</v>
       </c>
       <c r="B34" t="n">
         <v>79209</v>
@@ -4148,10 +4148,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>408522</v>
+        <v>408448</v>
       </c>
       <c r="R34" t="n">
-        <v>6772172</v>
+        <v>6772196</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4183,7 +4183,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4220,10 +4220,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130141178</v>
+        <v>130141042</v>
       </c>
       <c r="B35" t="n">
-        <v>79209</v>
+        <v>91759</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4231,21 +4231,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4255,10 +4255,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>408446</v>
+        <v>408420</v>
       </c>
       <c r="R35" t="n">
-        <v>6771720</v>
+        <v>6771911</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4290,7 +4290,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4300,7 +4300,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4327,45 +4327,54 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130141038</v>
+        <v>130141096</v>
       </c>
       <c r="B36" t="n">
-        <v>91722</v>
+        <v>98951</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>408067</v>
+        <v>408022</v>
       </c>
       <c r="R36" t="n">
-        <v>6772053</v>
+        <v>6772065</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4397,7 +4406,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4407,7 +4416,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4434,54 +4443,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130141096</v>
+        <v>130141038</v>
       </c>
       <c r="B37" t="n">
-        <v>98950</v>
+        <v>91723</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>408022</v>
+        <v>408067</v>
       </c>
       <c r="R37" t="n">
-        <v>6772065</v>
+        <v>6772053</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4513,7 +4513,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4523,7 +4523,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4550,7 +4550,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130141136</v>
+        <v>130141175</v>
       </c>
       <c r="B38" t="n">
         <v>79209</v>
@@ -4585,10 +4585,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>408031</v>
+        <v>408404</v>
       </c>
       <c r="R38" t="n">
-        <v>6772025</v>
+        <v>6771749</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4620,7 +4620,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4630,7 +4630,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4657,7 +4657,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130141175</v>
+        <v>130141136</v>
       </c>
       <c r="B39" t="n">
         <v>79209</v>
@@ -4692,10 +4692,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>408404</v>
+        <v>408031</v>
       </c>
       <c r="R39" t="n">
-        <v>6771749</v>
+        <v>6772025</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4727,7 +4727,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4764,10 +4764,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130141108</v>
+        <v>130141052</v>
       </c>
       <c r="B40" t="n">
-        <v>91778</v>
+        <v>57849</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4775,30 +4775,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>408452</v>
+        <v>408232</v>
       </c>
       <c r="R40" t="n">
-        <v>6771915</v>
+        <v>6771944</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4830,7 +4839,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4840,7 +4849,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4867,45 +4876,54 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130141113</v>
+        <v>130141101</v>
       </c>
       <c r="B41" t="n">
-        <v>79209</v>
+        <v>98951</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>408416</v>
+        <v>408032</v>
       </c>
       <c r="R41" t="n">
-        <v>6771941</v>
+        <v>6772075</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4937,7 +4955,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4947,7 +4965,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4974,10 +4992,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130141052</v>
+        <v>130141108</v>
       </c>
       <c r="B42" t="n">
-        <v>57849</v>
+        <v>91779</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4985,39 +5003,30 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>408232</v>
+        <v>408452</v>
       </c>
       <c r="R42" t="n">
-        <v>6771944</v>
+        <v>6771915</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5049,7 +5058,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5059,7 +5068,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5086,54 +5095,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130141101</v>
+        <v>130141113</v>
       </c>
       <c r="B43" t="n">
-        <v>98950</v>
+        <v>79209</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>408032</v>
+        <v>408416</v>
       </c>
       <c r="R43" t="n">
-        <v>6772075</v>
+        <v>6771941</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5165,7 +5165,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5175,7 +5175,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5202,50 +5202,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130141029</v>
+        <v>130141060</v>
       </c>
       <c r="B44" t="n">
-        <v>5197</v>
+        <v>92212</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>105930</v>
+        <v>1209</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>408243</v>
+        <v>408215</v>
       </c>
       <c r="R44" t="n">
-        <v>6771879</v>
+        <v>6771888</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5277,7 +5272,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5287,7 +5282,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5314,45 +5309,50 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130141060</v>
+        <v>130141029</v>
       </c>
       <c r="B45" t="n">
-        <v>92211</v>
+        <v>5197</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1209</v>
+        <v>105930</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>408215</v>
+        <v>408243</v>
       </c>
       <c r="R45" t="n">
-        <v>6771888</v>
+        <v>6771879</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5384,7 +5384,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5394,7 +5394,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5421,32 +5421,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130141105</v>
+        <v>130141103</v>
       </c>
       <c r="B46" t="n">
-        <v>91772</v>
+        <v>80280</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1204</v>
+        <v>229748</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5456,10 +5456,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>408032</v>
+        <v>408441</v>
       </c>
       <c r="R46" t="n">
-        <v>6772075</v>
+        <v>6771723</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5491,7 +5491,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5510,6 +5510,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5528,32 +5529,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130141073</v>
+        <v>130141128</v>
       </c>
       <c r="B47" t="n">
-        <v>80342</v>
+        <v>79209</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5563,10 +5564,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>408029</v>
+        <v>408213</v>
       </c>
       <c r="R47" t="n">
-        <v>6771956</v>
+        <v>6771880</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5598,7 +5599,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5608,7 +5609,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5849,7 +5850,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130141128</v>
+        <v>130141120</v>
       </c>
       <c r="B50" t="n">
         <v>79209</v>
@@ -5884,10 +5885,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>408213</v>
+        <v>408363</v>
       </c>
       <c r="R50" t="n">
-        <v>6771880</v>
+        <v>6771889</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5919,7 +5920,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5929,7 +5930,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5956,10 +5957,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130141120</v>
+        <v>130141105</v>
       </c>
       <c r="B51" t="n">
-        <v>79209</v>
+        <v>91773</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5967,21 +5968,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5991,10 +5992,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>408363</v>
+        <v>408032</v>
       </c>
       <c r="R51" t="n">
-        <v>6771889</v>
+        <v>6772075</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6026,7 +6027,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6036,7 +6037,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6063,10 +6064,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130141103</v>
+        <v>130141073</v>
       </c>
       <c r="B52" t="n">
-        <v>80280</v>
+        <v>80342</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6074,21 +6075,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>229748</v>
+        <v>6461</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6098,10 +6099,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>408441</v>
+        <v>408029</v>
       </c>
       <c r="R52" t="n">
-        <v>6771723</v>
+        <v>6771956</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6133,7 +6134,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6143,7 +6144,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6152,7 +6153,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6171,10 +6171,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130141107</v>
+        <v>130141196</v>
       </c>
       <c r="B53" t="n">
-        <v>91778</v>
+        <v>89153</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6182,19 +6182,23 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6202,10 +6206,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>408453</v>
+        <v>408233</v>
       </c>
       <c r="R53" t="n">
-        <v>6771936</v>
+        <v>6771921</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6237,7 +6241,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6247,7 +6251,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6277,7 +6281,7 @@
         <v>130141064</v>
       </c>
       <c r="B54" t="n">
-        <v>97821</v>
+        <v>97822</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6381,10 +6385,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130141196</v>
+        <v>130141107</v>
       </c>
       <c r="B55" t="n">
-        <v>89152</v>
+        <v>91779</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6392,23 +6396,19 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6416,10 +6416,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>408233</v>
+        <v>408453</v>
       </c>
       <c r="R55" t="n">
-        <v>6771921</v>
+        <v>6771936</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6451,7 +6451,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6488,7 +6488,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130141115</v>
+        <v>130141189</v>
       </c>
       <c r="B56" t="n">
         <v>79209</v>
@@ -6523,10 +6523,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>408423</v>
+        <v>408512</v>
       </c>
       <c r="R56" t="n">
-        <v>6771906</v>
+        <v>6772218</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6558,7 +6558,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6568,7 +6568,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6595,7 +6595,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130141189</v>
+        <v>130141135</v>
       </c>
       <c r="B57" t="n">
         <v>79209</v>
@@ -6630,10 +6630,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>408512</v>
+        <v>408031</v>
       </c>
       <c r="R57" t="n">
-        <v>6772218</v>
+        <v>6772014</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6665,7 +6665,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6675,7 +6675,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6702,7 +6702,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130141137</v>
+        <v>130141115</v>
       </c>
       <c r="B58" t="n">
         <v>79209</v>
@@ -6737,10 +6737,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>408034</v>
+        <v>408423</v>
       </c>
       <c r="R58" t="n">
-        <v>6772034</v>
+        <v>6771906</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6772,7 +6772,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6782,7 +6782,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6809,7 +6809,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130141135</v>
+        <v>130141117</v>
       </c>
       <c r="B59" t="n">
         <v>79209</v>
@@ -6844,10 +6844,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>408031</v>
+        <v>408409</v>
       </c>
       <c r="R59" t="n">
-        <v>6772014</v>
+        <v>6771881</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6916,7 +6916,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130141117</v>
+        <v>130141137</v>
       </c>
       <c r="B60" t="n">
         <v>79209</v>
@@ -6951,10 +6951,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>408409</v>
+        <v>408034</v>
       </c>
       <c r="R60" t="n">
-        <v>6771881</v>
+        <v>6772034</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6986,7 +6986,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6996,7 +6996,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7026,7 +7026,7 @@
         <v>130141195</v>
       </c>
       <c r="B61" t="n">
-        <v>89152</v>
+        <v>89153</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7130,32 +7130,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130141174</v>
+        <v>130141035</v>
       </c>
       <c r="B62" t="n">
-        <v>79209</v>
+        <v>91723</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7165,10 +7165,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>408396</v>
+        <v>408053</v>
       </c>
       <c r="R62" t="n">
-        <v>6771759</v>
+        <v>6772152</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7210,7 +7210,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7240,7 +7240,7 @@
         <v>130141040</v>
       </c>
       <c r="B63" t="n">
-        <v>91722</v>
+        <v>91723</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7344,32 +7344,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130141035</v>
+        <v>130141174</v>
       </c>
       <c r="B64" t="n">
-        <v>91722</v>
+        <v>79209</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7379,10 +7379,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>408053</v>
+        <v>408396</v>
       </c>
       <c r="R64" t="n">
-        <v>6772152</v>
+        <v>6771759</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7414,7 +7414,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7424,7 +7424,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7454,7 +7454,7 @@
         <v>130141071</v>
       </c>
       <c r="B65" t="n">
-        <v>97821</v>
+        <v>97822</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7665,54 +7665,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130141098</v>
+        <v>130141138</v>
       </c>
       <c r="B67" t="n">
-        <v>98950</v>
+        <v>79209</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>408080</v>
+        <v>408043</v>
       </c>
       <c r="R67" t="n">
-        <v>6772000</v>
+        <v>6772111</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7744,7 +7735,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7754,7 +7745,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7781,7 +7772,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130141119</v>
+        <v>130141112</v>
       </c>
       <c r="B68" t="n">
         <v>79209</v>
@@ -7816,10 +7807,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>408380</v>
+        <v>408432</v>
       </c>
       <c r="R68" t="n">
-        <v>6771903</v>
+        <v>6771948</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7851,7 +7842,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7861,7 +7852,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7888,7 +7879,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130141138</v>
+        <v>130141119</v>
       </c>
       <c r="B69" t="n">
         <v>79209</v>
@@ -7923,10 +7914,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>408043</v>
+        <v>408380</v>
       </c>
       <c r="R69" t="n">
-        <v>6772111</v>
+        <v>6771903</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7958,7 +7949,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7968,7 +7959,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7995,45 +7986,54 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130141112</v>
+        <v>130141098</v>
       </c>
       <c r="B70" t="n">
-        <v>79209</v>
+        <v>98951</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>408432</v>
+        <v>408080</v>
       </c>
       <c r="R70" t="n">
-        <v>6771948</v>
+        <v>6772000</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8065,7 +8065,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8102,32 +8102,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130141048</v>
+        <v>130141037</v>
       </c>
       <c r="B71" t="n">
-        <v>91758</v>
+        <v>91723</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8137,10 +8137,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>408067</v>
+        <v>408048</v>
       </c>
       <c r="R71" t="n">
-        <v>6772051</v>
+        <v>6772154</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8172,7 +8172,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8182,7 +8182,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8209,45 +8209,50 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130141037</v>
+        <v>130141055</v>
       </c>
       <c r="B72" t="n">
-        <v>91722</v>
+        <v>57849</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>408048</v>
+        <v>408062</v>
       </c>
       <c r="R72" t="n">
-        <v>6772154</v>
+        <v>6771974</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8279,7 +8284,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8289,7 +8294,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8316,10 +8321,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130141055</v>
+        <v>130141048</v>
       </c>
       <c r="B73" t="n">
-        <v>57849</v>
+        <v>91759</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8327,39 +8332,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>408062</v>
+        <v>408067</v>
       </c>
       <c r="R73" t="n">
-        <v>6771974</v>
+        <v>6772051</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8391,7 +8391,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8401,7 +8401,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8431,7 +8431,7 @@
         <v>130141070</v>
       </c>
       <c r="B74" t="n">
-        <v>97821</v>
+        <v>97822</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8535,10 +8535,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130141194</v>
+        <v>130141061</v>
       </c>
       <c r="B75" t="n">
-        <v>89152</v>
+        <v>57852</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8546,37 +8546,42 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>408303</v>
+        <v>408232</v>
       </c>
       <c r="R75" t="n">
-        <v>6771876</v>
+        <v>6771933</v>
       </c>
       <c r="S75" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8605,7 +8610,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8615,7 +8620,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8642,10 +8652,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130141116</v>
+        <v>130141194</v>
       </c>
       <c r="B76" t="n">
-        <v>79209</v>
+        <v>89153</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8653,21 +8663,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8677,13 +8687,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>408411</v>
+        <v>408303</v>
       </c>
       <c r="R76" t="n">
-        <v>6771863</v>
+        <v>6771876</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8712,7 +8722,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8722,7 +8732,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8749,32 +8759,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>130141181</v>
+        <v>130141069</v>
       </c>
       <c r="B77" t="n">
-        <v>79209</v>
+        <v>97822</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8784,10 +8794,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>408466</v>
+        <v>408016</v>
       </c>
       <c r="R77" t="n">
-        <v>6771845</v>
+        <v>6771944</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8819,7 +8829,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8829,7 +8839,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8856,32 +8866,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>130141183</v>
+        <v>130141063</v>
       </c>
       <c r="B78" t="n">
-        <v>79209</v>
+        <v>97822</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8891,10 +8901,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>408441</v>
+        <v>408291</v>
       </c>
       <c r="R78" t="n">
-        <v>6771967</v>
+        <v>6771923</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8926,7 +8936,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8936,7 +8946,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8963,7 +8973,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>130141129</v>
+        <v>130141181</v>
       </c>
       <c r="B79" t="n">
         <v>79209</v>
@@ -8998,10 +9008,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>408199</v>
+        <v>408466</v>
       </c>
       <c r="R79" t="n">
-        <v>6771896</v>
+        <v>6771845</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9033,7 +9043,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9043,7 +9053,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9070,10 +9080,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>130141061</v>
+        <v>130141129</v>
       </c>
       <c r="B80" t="n">
-        <v>57852</v>
+        <v>79209</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9081,39 +9091,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>408232</v>
+        <v>408199</v>
       </c>
       <c r="R80" t="n">
-        <v>6771933</v>
+        <v>6771896</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9145,7 +9150,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9155,12 +9160,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:16</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9187,32 +9187,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>130141063</v>
+        <v>130141116</v>
       </c>
       <c r="B81" t="n">
-        <v>97821</v>
+        <v>79209</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9222,10 +9222,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>408291</v>
+        <v>408411</v>
       </c>
       <c r="R81" t="n">
-        <v>6771923</v>
+        <v>6771863</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9257,7 +9257,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9294,32 +9294,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>130141069</v>
+        <v>130141183</v>
       </c>
       <c r="B82" t="n">
-        <v>97821</v>
+        <v>79209</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9329,10 +9329,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>408016</v>
+        <v>408441</v>
       </c>
       <c r="R82" t="n">
-        <v>6771944</v>
+        <v>6771967</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9364,7 +9364,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9374,7 +9374,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9511,7 +9511,7 @@
         <v>130141094</v>
       </c>
       <c r="B84" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9624,7 +9624,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>130141173</v>
+        <v>130141124</v>
       </c>
       <c r="B85" t="n">
         <v>79209</v>
@@ -9659,10 +9659,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>408388</v>
+        <v>408276</v>
       </c>
       <c r="R85" t="n">
-        <v>6771760</v>
+        <v>6771996</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9704,7 +9704,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9731,7 +9731,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>130141170</v>
+        <v>130141131</v>
       </c>
       <c r="B86" t="n">
         <v>79209</v>
@@ -9766,10 +9766,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>408080</v>
+        <v>408169</v>
       </c>
       <c r="R86" t="n">
-        <v>6772000</v>
+        <v>6771937</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9801,7 +9801,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9838,7 +9838,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>130141177</v>
+        <v>130141173</v>
       </c>
       <c r="B87" t="n">
         <v>79209</v>
@@ -9873,10 +9873,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>408429</v>
+        <v>408388</v>
       </c>
       <c r="R87" t="n">
-        <v>6771723</v>
+        <v>6771760</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9908,7 +9908,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9918,7 +9918,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9945,7 +9945,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>130141110</v>
+        <v>130141177</v>
       </c>
       <c r="B88" t="n">
         <v>79209</v>
@@ -9980,10 +9980,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>408466</v>
+        <v>408429</v>
       </c>
       <c r="R88" t="n">
-        <v>6771924</v>
+        <v>6771723</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10015,7 +10015,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10025,7 +10025,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10052,7 +10052,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>130141131</v>
+        <v>130141170</v>
       </c>
       <c r="B89" t="n">
         <v>79209</v>
@@ -10087,10 +10087,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>408169</v>
+        <v>408080</v>
       </c>
       <c r="R89" t="n">
-        <v>6771937</v>
+        <v>6772000</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10122,7 +10122,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10132,7 +10132,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10159,7 +10159,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>130141124</v>
+        <v>130141110</v>
       </c>
       <c r="B90" t="n">
         <v>79209</v>
@@ -10194,10 +10194,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>408276</v>
+        <v>408466</v>
       </c>
       <c r="R90" t="n">
-        <v>6771996</v>
+        <v>6771924</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10229,7 +10229,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10239,7 +10239,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD90" t="b">
